--- a/compare/output/dscale_CO2_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_CO2_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5.811287</v>
+        <v>5.806717</v>
       </c>
       <c r="F2" t="n">
-        <v>8.721392</v>
+        <v>8.717138</v>
       </c>
       <c r="G2" t="n">
-        <v>8.328682000000001</v>
+        <v>8.325889999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>7.765701</v>
+        <v>7.764017</v>
       </c>
       <c r="I2" t="n">
-        <v>6.974103</v>
+        <v>6.973333</v>
       </c>
       <c r="J2" t="n">
         <v>5.871501</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.060622</v>
+        <v>0.060618</v>
       </c>
       <c r="F3" t="n">
-        <v>0.124874</v>
+        <v>0.124848</v>
       </c>
       <c r="G3" t="n">
-        <v>0.155818</v>
+        <v>0.155789</v>
       </c>
       <c r="H3" t="n">
-        <v>0.179711</v>
+        <v>0.179685</v>
       </c>
       <c r="I3" t="n">
-        <v>0.184205</v>
+        <v>0.184191</v>
       </c>
       <c r="J3" t="n">
         <v>0.162066</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.008758999999999999</v>
+        <v>0.008963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.018877</v>
+        <v>0.019028</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02689</v>
+        <v>0.026976</v>
       </c>
       <c r="H4" t="n">
-        <v>0.032602</v>
+        <v>0.03265</v>
       </c>
       <c r="I4" t="n">
-        <v>0.032729</v>
+        <v>0.032749</v>
       </c>
       <c r="J4" t="n">
         <v>0.027987</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9910870000000001</v>
+        <v>0.990439</v>
       </c>
       <c r="F5" t="n">
-        <v>0.985665</v>
+        <v>0.985338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.544457</v>
+        <v>0.544423</v>
       </c>
       <c r="H5" t="n">
-        <v>0.343304</v>
+        <v>0.34335</v>
       </c>
       <c r="I5" t="n">
-        <v>0.239573</v>
+        <v>0.239611</v>
       </c>
       <c r="J5" t="n">
         <v>0.173622</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6.897741</v>
+        <v>6.895717</v>
       </c>
       <c r="F6" t="n">
-        <v>10.090136</v>
+        <v>10.088384</v>
       </c>
       <c r="G6" t="n">
-        <v>12.212664</v>
+        <v>12.210679</v>
       </c>
       <c r="H6" t="n">
-        <v>14.161863</v>
+        <v>14.160079</v>
       </c>
       <c r="I6" t="n">
-        <v>14.237911</v>
+        <v>14.236922</v>
       </c>
       <c r="J6" t="n">
         <v>12.508731</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.17246</v>
+        <v>1.176156</v>
       </c>
       <c r="F7" t="n">
-        <v>1.60998</v>
+        <v>1.613638</v>
       </c>
       <c r="G7" t="n">
-        <v>1.344796</v>
+        <v>1.347815</v>
       </c>
       <c r="H7" t="n">
-        <v>1.099601</v>
+        <v>1.101837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.850561</v>
+        <v>0.851725</v>
       </c>
       <c r="J7" t="n">
         <v>0.616183</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.272125</v>
+        <v>2.271189</v>
       </c>
       <c r="F8" t="n">
-        <v>3.424571</v>
+        <v>3.42371</v>
       </c>
       <c r="G8" t="n">
-        <v>3.276065</v>
+        <v>3.275585</v>
       </c>
       <c r="H8" t="n">
-        <v>3.040735</v>
+        <v>3.040506</v>
       </c>
       <c r="I8" t="n">
-        <v>2.643316</v>
+        <v>2.643238</v>
       </c>
       <c r="J8" t="n">
         <v>2.131325</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.001087</v>
+        <v>0.002133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00105</v>
+        <v>0.001813</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000916</v>
+        <v>0.001346</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000858</v>
+        <v>0.001088</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00075</v>
+        <v>0.000843</v>
       </c>
       <c r="J9" t="n">
         <v>0.000566</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.474799</v>
+        <v>0.474706</v>
       </c>
       <c r="F10" t="n">
-        <v>0.965632</v>
+        <v>0.965391</v>
       </c>
       <c r="G10" t="n">
-        <v>1.371638</v>
+        <v>1.371321</v>
       </c>
       <c r="H10" t="n">
-        <v>1.692546</v>
+        <v>1.692263</v>
       </c>
       <c r="I10" t="n">
-        <v>1.806579</v>
+        <v>1.806417</v>
       </c>
       <c r="J10" t="n">
         <v>1.668661</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.274767</v>
+        <v>0.280187</v>
       </c>
       <c r="F11" t="n">
-        <v>0.434908</v>
+        <v>0.439759</v>
       </c>
       <c r="G11" t="n">
-        <v>0.454084</v>
+        <v>0.457529</v>
       </c>
       <c r="H11" t="n">
-        <v>0.44286</v>
+        <v>0.445137</v>
       </c>
       <c r="I11" t="n">
-        <v>0.400143</v>
+        <v>0.401223</v>
       </c>
       <c r="J11" t="n">
         <v>0.338909</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.473091</v>
+        <v>3.470506</v>
       </c>
       <c r="F12" t="n">
-        <v>4.747392</v>
+        <v>4.745221</v>
       </c>
       <c r="G12" t="n">
-        <v>4.181093</v>
+        <v>4.179806</v>
       </c>
       <c r="H12" t="n">
-        <v>3.602412</v>
+        <v>3.601715</v>
       </c>
       <c r="I12" t="n">
-        <v>2.994761</v>
+        <v>2.994473</v>
       </c>
       <c r="J12" t="n">
         <v>2.287058</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.131522</v>
+        <v>1.132016</v>
       </c>
       <c r="F13" t="n">
-        <v>2.130988</v>
+        <v>2.131197</v>
       </c>
       <c r="G13" t="n">
-        <v>2.761547</v>
+        <v>2.761494</v>
       </c>
       <c r="H13" t="n">
-        <v>3.266475</v>
+        <v>3.266341</v>
       </c>
       <c r="I13" t="n">
-        <v>3.374555</v>
+        <v>3.374461</v>
       </c>
       <c r="J13" t="n">
         <v>3.059029</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44.330791</v>
+        <v>44.331956</v>
       </c>
       <c r="F14" t="n">
-        <v>52.154727</v>
+        <v>52.156986</v>
       </c>
       <c r="G14" t="n">
-        <v>54.181143</v>
+        <v>54.184473</v>
       </c>
       <c r="H14" t="n">
-        <v>55.417359</v>
+        <v>55.421845</v>
       </c>
       <c r="I14" t="n">
-        <v>53.561427</v>
+        <v>53.566822</v>
       </c>
       <c r="J14" t="n">
-        <v>50.740883</v>
+        <v>50.74693</v>
       </c>
       <c r="K14" t="n">
-        <v>48.625325</v>
+        <v>48.631906</v>
       </c>
       <c r="L14" t="n">
-        <v>47.238667</v>
+        <v>47.245718</v>
       </c>
       <c r="M14" t="n">
-        <v>46.378044</v>
+        <v>46.385584</v>
       </c>
       <c r="N14" t="n">
-        <v>45.037982</v>
+        <v>45.045957</v>
       </c>
       <c r="O14" t="n">
-        <v>42.730521</v>
+        <v>42.738817</v>
       </c>
       <c r="P14" t="n">
-        <v>39.622047</v>
+        <v>39.630533</v>
       </c>
       <c r="Q14" t="n">
-        <v>36.039024</v>
+        <v>36.047601</v>
       </c>
       <c r="R14" t="n">
-        <v>31.675723</v>
+        <v>31.684182</v>
       </c>
       <c r="S14" t="n">
-        <v>27.691063</v>
+        <v>27.699469</v>
       </c>
       <c r="T14" t="n">
-        <v>23.206732</v>
+        <v>23.21488</v>
       </c>
       <c r="U14" t="n">
-        <v>18.119987</v>
+        <v>18.127529</v>
       </c>
       <c r="V14" t="n">
-        <v>13.277448</v>
+        <v>13.284258</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.380015</v>
+        <v>64.379361</v>
       </c>
       <c r="F15" t="n">
-        <v>83.66168399999999</v>
+        <v>83.66107100000001</v>
       </c>
       <c r="G15" t="n">
-        <v>91.190428</v>
+        <v>91.190423</v>
       </c>
       <c r="H15" t="n">
-        <v>95.13732400000001</v>
+        <v>95.137958</v>
       </c>
       <c r="I15" t="n">
-        <v>92.265508</v>
+        <v>92.266473</v>
       </c>
       <c r="J15" t="n">
-        <v>87.023853</v>
+        <v>87.024854</v>
       </c>
       <c r="K15" t="n">
-        <v>83.00510300000001</v>
+        <v>83.00604</v>
       </c>
       <c r="L15" t="n">
-        <v>80.649359</v>
+        <v>80.650215</v>
       </c>
       <c r="M15" t="n">
-        <v>79.567677</v>
+        <v>79.568434</v>
       </c>
       <c r="N15" t="n">
-        <v>77.821046</v>
+        <v>77.82164899999999</v>
       </c>
       <c r="O15" t="n">
-        <v>74.365386</v>
+        <v>74.365802</v>
       </c>
       <c r="P15" t="n">
-        <v>69.376138</v>
+        <v>69.37637700000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.381192</v>
+        <v>63.381296</v>
       </c>
       <c r="R15" t="n">
-        <v>55.847424</v>
+        <v>55.847423</v>
       </c>
       <c r="S15" t="n">
-        <v>48.846559</v>
+        <v>48.846459</v>
       </c>
       <c r="T15" t="n">
-        <v>40.865339</v>
+        <v>40.865119</v>
       </c>
       <c r="U15" t="n">
-        <v>31.777761</v>
+        <v>31.777408</v>
       </c>
       <c r="V15" t="n">
-        <v>23.144612</v>
+        <v>23.144138</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.704223</v>
+        <v>14.705147</v>
       </c>
       <c r="F16" t="n">
-        <v>15.237874</v>
+        <v>15.239545</v>
       </c>
       <c r="G16" t="n">
-        <v>13.503128</v>
+        <v>13.505049</v>
       </c>
       <c r="H16" t="n">
-        <v>12.196672</v>
+        <v>12.198645</v>
       </c>
       <c r="I16" t="n">
-        <v>10.815522</v>
+        <v>10.817385</v>
       </c>
       <c r="J16" t="n">
-        <v>9.699239</v>
+        <v>9.700967</v>
       </c>
       <c r="K16" t="n">
-        <v>8.997764</v>
+        <v>8.999409</v>
       </c>
       <c r="L16" t="n">
-        <v>8.59525</v>
+        <v>8.596871999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>8.380482000000001</v>
+        <v>8.382132</v>
       </c>
       <c r="N16" t="n">
-        <v>8.116834000000001</v>
+        <v>8.118517000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>7.680668</v>
+        <v>7.68235</v>
       </c>
       <c r="P16" t="n">
-        <v>7.091587</v>
+        <v>7.093225</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41318</v>
+        <v>6.41474</v>
       </c>
       <c r="R16" t="n">
-        <v>5.600728</v>
+        <v>5.602174</v>
       </c>
       <c r="S16" t="n">
-        <v>4.866022</v>
+        <v>4.867375</v>
       </c>
       <c r="T16" t="n">
-        <v>4.054929</v>
+        <v>4.056171</v>
       </c>
       <c r="U16" t="n">
-        <v>3.150319</v>
+        <v>3.151415</v>
       </c>
       <c r="V16" t="n">
-        <v>2.297431</v>
+        <v>2.298379</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16.44449</v>
+        <v>16.443042</v>
       </c>
       <c r="F17" t="n">
-        <v>19.246752</v>
+        <v>19.243283</v>
       </c>
       <c r="G17" t="n">
-        <v>19.230247</v>
+        <v>19.224766</v>
       </c>
       <c r="H17" t="n">
-        <v>18.68007</v>
+        <v>18.672685</v>
       </c>
       <c r="I17" t="n">
-        <v>17.021707</v>
+        <v>17.013097</v>
       </c>
       <c r="J17" t="n">
-        <v>15.073479</v>
+        <v>15.064102</v>
       </c>
       <c r="K17" t="n">
-        <v>13.520092</v>
+        <v>13.510041</v>
       </c>
       <c r="L17" t="n">
-        <v>12.444436</v>
+        <v>12.433685</v>
       </c>
       <c r="M17" t="n">
-        <v>11.781746</v>
+        <v>11.770264</v>
       </c>
       <c r="N17" t="n">
-        <v>11.196053</v>
+        <v>11.184045</v>
       </c>
       <c r="O17" t="n">
-        <v>10.499551</v>
+        <v>10.487345</v>
       </c>
       <c r="P17" t="n">
-        <v>9.673776</v>
+        <v>9.661659999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.761877</v>
+        <v>8.750007</v>
       </c>
       <c r="R17" t="n">
-        <v>7.685731</v>
+        <v>7.674369</v>
       </c>
       <c r="S17" t="n">
-        <v>6.728527</v>
+        <v>6.717552</v>
       </c>
       <c r="T17" t="n">
-        <v>5.674747</v>
+        <v>5.664416</v>
       </c>
       <c r="U17" t="n">
-        <v>4.48588</v>
+        <v>4.47661</v>
       </c>
       <c r="V17" t="n">
-        <v>3.344428</v>
+        <v>3.336324</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.260662</v>
+        <v>8.260675000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>10.479172</v>
+        <v>10.479323</v>
       </c>
       <c r="G18" t="n">
-        <v>10.813144</v>
+        <v>10.813378</v>
       </c>
       <c r="H18" t="n">
-        <v>10.801656</v>
+        <v>10.801948</v>
       </c>
       <c r="I18" t="n">
-        <v>10.278578</v>
+        <v>10.278966</v>
       </c>
       <c r="J18" t="n">
-        <v>9.811574</v>
+        <v>9.812175999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>9.61004</v>
+        <v>9.610929</v>
       </c>
       <c r="L18" t="n">
-        <v>9.627133000000001</v>
+        <v>9.628356</v>
       </c>
       <c r="M18" t="n">
-        <v>9.685060999999999</v>
+        <v>9.686598</v>
       </c>
       <c r="N18" t="n">
-        <v>9.4848</v>
+        <v>9.486547</v>
       </c>
       <c r="O18" t="n">
-        <v>8.908199</v>
+        <v>8.91001</v>
       </c>
       <c r="P18" t="n">
-        <v>8.065322999999999</v>
+        <v>8.067076999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.109472</v>
+        <v>7.111102</v>
       </c>
       <c r="R18" t="n">
-        <v>6.041074</v>
+        <v>6.042533</v>
       </c>
       <c r="S18" t="n">
-        <v>5.109797</v>
+        <v>5.111111</v>
       </c>
       <c r="T18" t="n">
-        <v>4.153438</v>
+        <v>4.154598</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15407</v>
+        <v>3.155055</v>
       </c>
       <c r="V18" t="n">
-        <v>2.252426</v>
+        <v>2.253246</v>
       </c>
     </row>
     <row r="19">
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.010451</v>
+        <v>0.011424</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01579</v>
+        <v>0.016624</v>
       </c>
       <c r="G19" t="n">
-        <v>0.025147</v>
+        <v>0.025957</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04201</v>
+        <v>0.042817</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06296300000000001</v>
+        <v>0.063553</v>
       </c>
       <c r="J19" t="n">
         <v>0.079482</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.000408</v>
+        <v>0.000617</v>
       </c>
       <c r="F20" t="n">
-        <v>0.000396</v>
+        <v>0.000568</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000407</v>
+        <v>0.000576</v>
       </c>
       <c r="H20" t="n">
-        <v>0.000446</v>
+        <v>0.000611</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000432</v>
+        <v>0.000547</v>
       </c>
       <c r="J20" t="n">
         <v>0.000313</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.020226</v>
+        <v>0.020241</v>
       </c>
       <c r="F21" t="n">
-        <v>0.038301</v>
+        <v>0.038311</v>
       </c>
       <c r="G21" t="n">
-        <v>0.066453</v>
+        <v>0.066458</v>
       </c>
       <c r="H21" t="n">
-        <v>0.107985</v>
+        <v>0.107987</v>
       </c>
       <c r="I21" t="n">
-        <v>0.146862</v>
+        <v>0.146861</v>
       </c>
       <c r="J21" t="n">
         <v>0.163592</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.465203</v>
+        <v>0.465342</v>
       </c>
       <c r="F22" t="n">
-        <v>0.623856</v>
+        <v>0.62398</v>
       </c>
       <c r="G22" t="n">
-        <v>0.877441</v>
+        <v>0.877549</v>
       </c>
       <c r="H22" t="n">
-        <v>1.341634</v>
+        <v>1.341715</v>
       </c>
       <c r="I22" t="n">
-        <v>1.877985</v>
+        <v>1.878012</v>
       </c>
       <c r="J22" t="n">
         <v>2.233047</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.553486</v>
+        <v>0.553569</v>
       </c>
       <c r="F23" t="n">
-        <v>0.758559</v>
+        <v>0.758643</v>
       </c>
       <c r="G23" t="n">
-        <v>1.045782</v>
+        <v>1.045861</v>
       </c>
       <c r="H23" t="n">
-        <v>1.519123</v>
+        <v>1.51919</v>
       </c>
       <c r="I23" t="n">
-        <v>2.024056</v>
+        <v>2.024088</v>
       </c>
       <c r="J23" t="n">
         <v>2.335641</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.001006</v>
+        <v>0.001128</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001343</v>
+        <v>0.001441</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001767</v>
+        <v>0.00186</v>
       </c>
       <c r="H24" t="n">
-        <v>0.002483</v>
+        <v>0.002573</v>
       </c>
       <c r="I24" t="n">
-        <v>0.003186</v>
+        <v>0.003251</v>
       </c>
       <c r="J24" t="n">
         <v>0.003507</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.001115</v>
+        <v>0.001144</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00187</v>
+        <v>0.001892</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002871</v>
+        <v>0.00289</v>
       </c>
       <c r="H25" t="n">
-        <v>0.004289</v>
+        <v>0.004306</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0056</v>
+        <v>0.005612</v>
       </c>
       <c r="J25" t="n">
         <v>0.006256</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.392522</v>
+        <v>0.392867</v>
       </c>
       <c r="F26" t="n">
-        <v>0.670786</v>
+        <v>0.671064</v>
       </c>
       <c r="G26" t="n">
-        <v>1.216674</v>
+        <v>1.216896</v>
       </c>
       <c r="H26" t="n">
-        <v>2.253636</v>
+        <v>2.253786</v>
       </c>
       <c r="I26" t="n">
-        <v>3.680493</v>
+        <v>3.680523</v>
       </c>
       <c r="J26" t="n">
         <v>4.98581</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.035477</v>
+        <v>0.035629</v>
       </c>
       <c r="F27" t="n">
-        <v>0.059448</v>
+        <v>0.059577</v>
       </c>
       <c r="G27" t="n">
-        <v>0.106201</v>
+        <v>0.106318</v>
       </c>
       <c r="H27" t="n">
-        <v>0.194989</v>
+        <v>0.195099</v>
       </c>
       <c r="I27" t="n">
-        <v>0.313211</v>
+        <v>0.313284</v>
       </c>
       <c r="J27" t="n">
         <v>0.414603</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22.294484</v>
+        <v>22.292417</v>
       </c>
       <c r="F28" t="n">
-        <v>31.451362</v>
+        <v>31.449611</v>
       </c>
       <c r="G28" t="n">
-        <v>31.925888</v>
+        <v>31.924265</v>
       </c>
       <c r="H28" t="n">
-        <v>30.501211</v>
+        <v>30.499723</v>
       </c>
       <c r="I28" t="n">
-        <v>25.550375</v>
+        <v>25.549433</v>
       </c>
       <c r="J28" t="n">
         <v>19.296514</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7298210000000001</v>
+        <v>0.768377</v>
       </c>
       <c r="F29" t="n">
-        <v>1.542907</v>
+        <v>1.557879</v>
       </c>
       <c r="G29" t="n">
-        <v>1.988008</v>
+        <v>1.991405</v>
       </c>
       <c r="H29" t="n">
-        <v>2.153879</v>
+        <v>2.155247</v>
       </c>
       <c r="I29" t="n">
-        <v>2.153762</v>
+        <v>2.154075</v>
       </c>
       <c r="J29" t="n">
         <v>2.119357</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.247535</v>
+        <v>2.171741</v>
       </c>
       <c r="F30" t="n">
-        <v>7.310869</v>
+        <v>7.041584</v>
       </c>
       <c r="G30" t="n">
-        <v>14.329418</v>
+        <v>13.917203</v>
       </c>
       <c r="H30" t="n">
-        <v>20.343877</v>
+        <v>19.963961</v>
       </c>
       <c r="I30" t="n">
-        <v>23.578148</v>
+        <v>23.351579</v>
       </c>
       <c r="J30" t="n">
         <v>24.799385</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.758136</v>
+        <v>0.717467</v>
       </c>
       <c r="F31" t="n">
-        <v>1.613837</v>
+        <v>1.547765</v>
       </c>
       <c r="G31" t="n">
-        <v>2.207751</v>
+        <v>2.142141</v>
       </c>
       <c r="H31" t="n">
-        <v>2.440682</v>
+        <v>2.394511</v>
       </c>
       <c r="I31" t="n">
-        <v>2.446054</v>
+        <v>2.422396</v>
       </c>
       <c r="J31" t="n">
         <v>2.394707</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.269108</v>
+        <v>1.352349</v>
       </c>
       <c r="F32" t="n">
-        <v>2.956989</v>
+        <v>2.969362</v>
       </c>
       <c r="G32" t="n">
-        <v>4.31569</v>
+        <v>4.280629</v>
       </c>
       <c r="H32" t="n">
-        <v>4.990439</v>
+        <v>4.953456</v>
       </c>
       <c r="I32" t="n">
-        <v>5.059901</v>
+        <v>5.038373</v>
       </c>
       <c r="J32" t="n">
         <v>4.903482</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.703804</v>
+        <v>0.790751</v>
       </c>
       <c r="F33" t="n">
-        <v>1.408775</v>
+        <v>1.471882</v>
       </c>
       <c r="G33" t="n">
-        <v>1.774857</v>
+        <v>1.814322</v>
       </c>
       <c r="H33" t="n">
-        <v>1.872149</v>
+        <v>1.896703</v>
       </c>
       <c r="I33" t="n">
-        <v>1.822075</v>
+        <v>1.833683</v>
       </c>
       <c r="J33" t="n">
         <v>1.761432</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>28.388205</v>
+        <v>26.793345</v>
       </c>
       <c r="F34" t="n">
-        <v>25.877124</v>
+        <v>24.850605</v>
       </c>
       <c r="G34" t="n">
-        <v>15.084454</v>
+        <v>14.72749</v>
       </c>
       <c r="H34" t="n">
-        <v>9.512473999999999</v>
+        <v>9.427011</v>
       </c>
       <c r="I34" t="n">
-        <v>6.776775</v>
+        <v>6.771002</v>
       </c>
       <c r="J34" t="n">
         <v>5.521641</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.131599</v>
+        <v>0.203969</v>
       </c>
       <c r="F35" t="n">
-        <v>0.182802</v>
+        <v>0.271383</v>
       </c>
       <c r="G35" t="n">
-        <v>0.173187</v>
+        <v>0.257512</v>
       </c>
       <c r="H35" t="n">
-        <v>0.145923</v>
+        <v>0.208671</v>
       </c>
       <c r="I35" t="n">
-        <v>0.116768</v>
+        <v>0.149271</v>
       </c>
       <c r="J35" t="n">
         <v>0.09263299999999999</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.010989</v>
+        <v>0.02126</v>
       </c>
       <c r="F36" t="n">
-        <v>0.012741</v>
+        <v>0.022905</v>
       </c>
       <c r="G36" t="n">
-        <v>0.011486</v>
+        <v>0.01845</v>
       </c>
       <c r="H36" t="n">
-        <v>0.009830999999999999</v>
+        <v>0.013736</v>
       </c>
       <c r="I36" t="n">
-        <v>0.008355</v>
+        <v>0.009993999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0.007067</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.06976599999999999</v>
+        <v>0.155317</v>
       </c>
       <c r="F37" t="n">
-        <v>0.063264</v>
+        <v>0.137222</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04779</v>
+        <v>0.097806</v>
       </c>
       <c r="H37" t="n">
-        <v>0.034199</v>
+        <v>0.063705</v>
       </c>
       <c r="I37" t="n">
-        <v>0.023009</v>
+        <v>0.036352</v>
       </c>
       <c r="J37" t="n">
         <v>0.013816</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.392016</v>
+        <v>1.531069</v>
       </c>
       <c r="F38" t="n">
-        <v>2.703299</v>
+        <v>2.809599</v>
       </c>
       <c r="G38" t="n">
-        <v>3.57708</v>
+        <v>3.635977</v>
       </c>
       <c r="H38" t="n">
-        <v>3.982152</v>
+        <v>4.01423</v>
       </c>
       <c r="I38" t="n">
-        <v>4.011332</v>
+        <v>4.025687</v>
       </c>
       <c r="J38" t="n">
         <v>3.899444</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.323022</v>
+        <v>1.286012</v>
       </c>
       <c r="F39" t="n">
-        <v>3.161114</v>
+        <v>3.060855</v>
       </c>
       <c r="G39" t="n">
-        <v>4.422402</v>
+        <v>4.311632</v>
       </c>
       <c r="H39" t="n">
-        <v>4.915762</v>
+        <v>4.835674</v>
       </c>
       <c r="I39" t="n">
-        <v>4.85445</v>
+        <v>4.813702</v>
       </c>
       <c r="J39" t="n">
         <v>4.646435</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.138965</v>
+        <v>0.135921</v>
       </c>
       <c r="F40" t="n">
-        <v>0.285396</v>
+        <v>0.278043</v>
       </c>
       <c r="G40" t="n">
-        <v>0.366452</v>
+        <v>0.358865</v>
       </c>
       <c r="H40" t="n">
-        <v>0.402229</v>
+        <v>0.396711</v>
       </c>
       <c r="I40" t="n">
-        <v>0.402459</v>
+        <v>0.399564</v>
       </c>
       <c r="J40" t="n">
         <v>0.39913</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.058087</v>
+        <v>0.06174</v>
       </c>
       <c r="F41" t="n">
-        <v>0.103577</v>
+        <v>0.106796</v>
       </c>
       <c r="G41" t="n">
-        <v>0.130408</v>
+        <v>0.13242</v>
       </c>
       <c r="H41" t="n">
-        <v>0.14353</v>
+        <v>0.144647</v>
       </c>
       <c r="I41" t="n">
-        <v>0.147414</v>
+        <v>0.147837</v>
       </c>
       <c r="J41" t="n">
         <v>0.149906</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.056641</v>
+        <v>0.128578</v>
       </c>
       <c r="F42" t="n">
-        <v>0.053177</v>
+        <v>0.122044</v>
       </c>
       <c r="G42" t="n">
-        <v>0.039296</v>
+        <v>0.090611</v>
       </c>
       <c r="H42" t="n">
-        <v>0.024988</v>
+        <v>0.057451</v>
       </c>
       <c r="I42" t="n">
-        <v>0.012473</v>
+        <v>0.027903</v>
       </c>
       <c r="J42" t="n">
         <v>0.001468</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.52577</v>
+        <v>1.454461</v>
       </c>
       <c r="F43" t="n">
-        <v>2.396559</v>
+        <v>2.316234</v>
       </c>
       <c r="G43" t="n">
-        <v>2.447943</v>
+        <v>2.394557</v>
       </c>
       <c r="H43" t="n">
-        <v>2.233097</v>
+        <v>2.206723</v>
       </c>
       <c r="I43" t="n">
-        <v>1.994932</v>
+        <v>1.98471</v>
       </c>
       <c r="J43" t="n">
         <v>1.836611</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.274548</v>
+        <v>1.249512</v>
       </c>
       <c r="F44" t="n">
-        <v>2.672006</v>
+        <v>2.608776</v>
       </c>
       <c r="G44" t="n">
-        <v>3.493611</v>
+        <v>3.427914</v>
       </c>
       <c r="H44" t="n">
-        <v>3.7918</v>
+        <v>3.746746</v>
       </c>
       <c r="I44" t="n">
-        <v>3.781473</v>
+        <v>3.75879</v>
       </c>
       <c r="J44" t="n">
         <v>3.720736</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.138279</v>
+        <v>0.168344</v>
       </c>
       <c r="F45" t="n">
-        <v>0.237362</v>
+        <v>0.267596</v>
       </c>
       <c r="G45" t="n">
-        <v>0.281038</v>
+        <v>0.304571</v>
       </c>
       <c r="H45" t="n">
-        <v>0.293183</v>
+        <v>0.308689</v>
       </c>
       <c r="I45" t="n">
-        <v>0.28638</v>
+        <v>0.293934</v>
       </c>
       <c r="J45" t="n">
         <v>0.275617</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.246215</v>
+        <v>4.030581</v>
       </c>
       <c r="F46" t="n">
-        <v>10.258571</v>
+        <v>9.850009999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>14.855622</v>
+        <v>14.42463</v>
       </c>
       <c r="H46" t="n">
-        <v>17.332441</v>
+        <v>17.012969</v>
       </c>
       <c r="I46" t="n">
-        <v>17.242334</v>
+        <v>17.081302</v>
       </c>
       <c r="J46" t="n">
         <v>16.407804</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.866704</v>
+        <v>5.278977</v>
       </c>
       <c r="F47" t="n">
-        <v>5.950673</v>
+        <v>7.586726</v>
       </c>
       <c r="G47" t="n">
-        <v>6.812279</v>
+        <v>8.17215</v>
       </c>
       <c r="H47" t="n">
-        <v>7.032106</v>
+        <v>7.975842</v>
       </c>
       <c r="I47" t="n">
-        <v>6.830899</v>
+        <v>7.320552</v>
       </c>
       <c r="J47" t="n">
         <v>6.504728</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.635532</v>
+        <v>0.726969</v>
       </c>
       <c r="F48" t="n">
-        <v>1.303529</v>
+        <v>1.375406</v>
       </c>
       <c r="G48" t="n">
-        <v>1.750717</v>
+        <v>1.795424</v>
       </c>
       <c r="H48" t="n">
-        <v>2.0158</v>
+        <v>2.040488</v>
       </c>
       <c r="I48" t="n">
-        <v>2.164656</v>
+        <v>2.174073</v>
       </c>
       <c r="J48" t="n">
         <v>2.304599</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.472225</v>
+        <v>0.458999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8964</v>
+        <v>0.87287</v>
       </c>
       <c r="G49" t="n">
-        <v>1.134353</v>
+        <v>1.111166</v>
       </c>
       <c r="H49" t="n">
-        <v>1.253178</v>
+        <v>1.23633</v>
       </c>
       <c r="I49" t="n">
-        <v>1.303408</v>
+        <v>1.294081</v>
       </c>
       <c r="J49" t="n">
         <v>1.336605</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.00549</v>
+        <v>0.007112</v>
       </c>
       <c r="F50" t="n">
-        <v>0.008958000000000001</v>
+        <v>0.010493</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01078</v>
+        <v>0.011831</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0116</v>
+        <v>0.012201</v>
       </c>
       <c r="I50" t="n">
-        <v>0.011721</v>
+        <v>0.011974</v>
       </c>
       <c r="J50" t="n">
         <v>0.011536</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.565422</v>
+        <v>0.554973</v>
       </c>
       <c r="F51" t="n">
-        <v>1.354032</v>
+        <v>1.317091</v>
       </c>
       <c r="G51" t="n">
-        <v>1.988932</v>
+        <v>1.943498</v>
       </c>
       <c r="H51" t="n">
-        <v>2.400599</v>
+        <v>2.363835</v>
       </c>
       <c r="I51" t="n">
-        <v>2.604481</v>
+        <v>2.583442</v>
       </c>
       <c r="J51" t="n">
         <v>2.723999</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.06118</v>
+        <v>1.021237</v>
       </c>
       <c r="F52" t="n">
-        <v>2.743197</v>
+        <v>2.644033</v>
       </c>
       <c r="G52" t="n">
-        <v>4.265751</v>
+        <v>4.147101</v>
       </c>
       <c r="H52" t="n">
-        <v>5.183832</v>
+        <v>5.090216</v>
       </c>
       <c r="I52" t="n">
-        <v>5.475329</v>
+        <v>5.424314</v>
       </c>
       <c r="J52" t="n">
         <v>5.451573</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>78.289241</v>
+        <v>78.328422</v>
       </c>
       <c r="F54" t="n">
-        <v>89.41142600000001</v>
+        <v>89.44839399999999</v>
       </c>
       <c r="G54" t="n">
-        <v>86.73409100000001</v>
+        <v>86.771068</v>
       </c>
       <c r="H54" t="n">
-        <v>76.35602400000001</v>
+        <v>76.38974</v>
       </c>
       <c r="I54" t="n">
-        <v>62.017179</v>
+        <v>62.044672</v>
       </c>
       <c r="J54" t="n">
-        <v>51.455047</v>
+        <v>51.477296</v>
       </c>
       <c r="K54" t="n">
-        <v>42.817327</v>
+        <v>42.835056</v>
       </c>
       <c r="L54" t="n">
-        <v>37.016821</v>
+        <v>37.031289</v>
       </c>
       <c r="M54" t="n">
-        <v>33.668312</v>
+        <v>33.68064</v>
       </c>
       <c r="N54" t="n">
-        <v>31.203965</v>
+        <v>31.214632</v>
       </c>
       <c r="O54" t="n">
-        <v>27.427094</v>
+        <v>27.435873</v>
       </c>
       <c r="P54" t="n">
-        <v>19.794112</v>
+        <v>19.800027</v>
       </c>
       <c r="Q54" t="n">
-        <v>9.669814000000001</v>
+        <v>9.672491000000001</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.321099</v>
+        <v>-1.321433</v>
       </c>
       <c r="S54" t="n">
-        <v>-12.207848</v>
+        <v>-12.210625</v>
       </c>
       <c r="T54" t="n">
-        <v>-21.970041</v>
+        <v>-21.974442</v>
       </c>
       <c r="U54" t="n">
-        <v>-30.59238</v>
+        <v>-30.597658</v>
       </c>
       <c r="V54" t="n">
-        <v>-37.203927</v>
+        <v>-37.209266</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>43.871183</v>
+        <v>43.832002</v>
       </c>
       <c r="F55" t="n">
-        <v>55.498979</v>
+        <v>55.462011</v>
       </c>
       <c r="G55" t="n">
-        <v>57.479109</v>
+        <v>57.442132</v>
       </c>
       <c r="H55" t="n">
-        <v>52.399099</v>
+        <v>52.365383</v>
       </c>
       <c r="I55" t="n">
-        <v>43.033681</v>
+        <v>43.006189</v>
       </c>
       <c r="J55" t="n">
-        <v>35.395925</v>
+        <v>35.373676</v>
       </c>
       <c r="K55" t="n">
-        <v>28.780975</v>
+        <v>28.763246</v>
       </c>
       <c r="L55" t="n">
-        <v>24.063729</v>
+        <v>24.049262</v>
       </c>
       <c r="M55" t="n">
-        <v>21.058853</v>
+        <v>21.046524</v>
       </c>
       <c r="N55" t="n">
-        <v>18.735968</v>
+        <v>18.725301</v>
       </c>
       <c r="O55" t="n">
-        <v>15.852451</v>
+        <v>15.843672</v>
       </c>
       <c r="P55" t="n">
-        <v>11.033116</v>
+        <v>11.027201</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.201725</v>
+        <v>5.199048</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.685551</v>
+        <v>-0.685217</v>
       </c>
       <c r="S55" t="n">
-        <v>-6.106289</v>
+        <v>-6.103512</v>
       </c>
       <c r="T55" t="n">
-        <v>-10.607515</v>
+        <v>-10.603114</v>
       </c>
       <c r="U55" t="n">
-        <v>-14.347641</v>
+        <v>-14.342363</v>
       </c>
       <c r="V55" t="n">
-        <v>-17.000252</v>
+        <v>-16.994914</v>
       </c>
     </row>
     <row r="56">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.000187</v>
+        <v>0.000188</v>
       </c>
       <c r="F58" t="n">
-        <v>0.00024</v>
+        <v>0.000241</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000272</v>
+        <v>0.000273</v>
       </c>
       <c r="H58" t="n">
         <v>0.000286</v>
@@ -4937,7 +4937,7 @@
         <v>0.000397</v>
       </c>
       <c r="F60" t="n">
-        <v>0.000766</v>
+        <v>0.000767</v>
       </c>
       <c r="G60" t="n">
         <v>0.001328</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.038827</v>
+        <v>0.038836</v>
       </c>
       <c r="F61" t="n">
-        <v>0.052269</v>
+        <v>0.052275</v>
       </c>
       <c r="G61" t="n">
-        <v>0.071668</v>
+        <v>0.071671</v>
       </c>
       <c r="H61" t="n">
-        <v>0.092251</v>
+        <v>0.092254</v>
       </c>
       <c r="I61" t="n">
-        <v>0.104359</v>
+        <v>0.104361</v>
       </c>
       <c r="J61" t="n">
         <v>0.102946</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.055692</v>
+        <v>0.055727</v>
       </c>
       <c r="F62" t="n">
-        <v>0.045536</v>
+        <v>0.045559</v>
       </c>
       <c r="G62" t="n">
-        <v>0.042017</v>
+        <v>0.042034</v>
       </c>
       <c r="H62" t="n">
-        <v>0.040675</v>
+        <v>0.040686</v>
       </c>
       <c r="I62" t="n">
-        <v>0.037463</v>
+        <v>0.037468</v>
       </c>
       <c r="J62" t="n">
         <v>0.031896</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.09417</v>
+        <v>0.094199</v>
       </c>
       <c r="F63" t="n">
-        <v>0.106598</v>
+        <v>0.106615</v>
       </c>
       <c r="G63" t="n">
-        <v>0.13714</v>
+        <v>0.137152</v>
       </c>
       <c r="H63" t="n">
-        <v>0.167721</v>
+        <v>0.167729</v>
       </c>
       <c r="I63" t="n">
-        <v>0.176563</v>
+        <v>0.176567</v>
       </c>
       <c r="J63" t="n">
         <v>0.157522</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.776694</v>
+        <v>0.776712</v>
       </c>
       <c r="F65" t="n">
-        <v>1.020607</v>
+        <v>1.020618</v>
       </c>
       <c r="G65" t="n">
-        <v>1.318545</v>
+        <v>1.318554</v>
       </c>
       <c r="H65" t="n">
-        <v>1.612477</v>
+        <v>1.612483</v>
       </c>
       <c r="I65" t="n">
-        <v>1.73775</v>
+        <v>1.737753</v>
       </c>
       <c r="J65" t="n">
         <v>1.673627</v>
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.054643</v>
+        <v>2.054649</v>
       </c>
       <c r="F66" t="n">
-        <v>2.661267</v>
+        <v>2.66127</v>
       </c>
       <c r="G66" t="n">
-        <v>3.359163</v>
+        <v>3.359165</v>
       </c>
       <c r="H66" t="n">
-        <v>3.999257</v>
+        <v>3.999258</v>
       </c>
       <c r="I66" t="n">
         <v>4.207941</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>45.994548</v>
+        <v>45.994394</v>
       </c>
       <c r="F67" t="n">
-        <v>47.594758</v>
+        <v>47.594668</v>
       </c>
       <c r="G67" t="n">
-        <v>45.138995</v>
+        <v>45.138937</v>
       </c>
       <c r="H67" t="n">
-        <v>41.137296</v>
+        <v>41.13726</v>
       </c>
       <c r="I67" t="n">
-        <v>33.993776</v>
+        <v>33.99376</v>
       </c>
       <c r="J67" t="n">
         <v>25.600703</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.042431</v>
+        <v>0.04244</v>
       </c>
       <c r="F68" t="n">
-        <v>0.034477</v>
+        <v>0.034482</v>
       </c>
       <c r="G68" t="n">
-        <v>0.024269</v>
+        <v>0.024274</v>
       </c>
       <c r="H68" t="n">
-        <v>0.018003</v>
+        <v>0.018006</v>
       </c>
       <c r="I68" t="n">
-        <v>0.013799</v>
+        <v>0.013801</v>
       </c>
       <c r="J68" t="n">
         <v>0.010698</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.410315</v>
+        <v>7.410296</v>
       </c>
       <c r="F70" t="n">
-        <v>8.621919</v>
+        <v>8.621905999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>9.503354</v>
+        <v>9.503344</v>
       </c>
       <c r="H70" t="n">
-        <v>9.922466999999999</v>
+        <v>9.922459999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>9.204209000000001</v>
+        <v>9.204205999999999</v>
       </c>
       <c r="J70" t="n">
         <v>7.572541</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.025531</v>
+        <v>0.025544</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02406</v>
+        <v>0.024068</v>
       </c>
       <c r="G71" t="n">
-        <v>0.028336</v>
+        <v>0.028342</v>
       </c>
       <c r="H71" t="n">
-        <v>0.034983</v>
+        <v>0.034987</v>
       </c>
       <c r="I71" t="n">
-        <v>0.039695</v>
+        <v>0.039697</v>
       </c>
       <c r="J71" t="n">
         <v>0.039267</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.312261</v>
+        <v>0.312269</v>
       </c>
       <c r="F72" t="n">
-        <v>0.404538</v>
+        <v>0.404542</v>
       </c>
       <c r="G72" t="n">
-        <v>0.487281</v>
+        <v>0.487284</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5337809999999999</v>
+        <v>0.533782</v>
       </c>
       <c r="I72" t="n">
-        <v>0.498876</v>
+        <v>0.498877</v>
       </c>
       <c r="J72" t="n">
         <v>0.403938</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.000526</v>
+        <v>0.00057</v>
       </c>
       <c r="F73" t="n">
-        <v>0.001082</v>
+        <v>0.001103</v>
       </c>
       <c r="G73" t="n">
-        <v>0.002939</v>
+        <v>0.002949</v>
       </c>
       <c r="H73" t="n">
-        <v>0.006275</v>
+        <v>0.00628</v>
       </c>
       <c r="I73" t="n">
-        <v>0.00861</v>
+        <v>0.008613000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0.008258</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2.1995</v>
+        <v>2.041557</v>
       </c>
       <c r="F75" t="n">
-        <v>2.466336</v>
+        <v>2.251528</v>
       </c>
       <c r="G75" t="n">
-        <v>2.510376</v>
+        <v>2.282952</v>
       </c>
       <c r="H75" t="n">
-        <v>2.260262</v>
+        <v>2.021128</v>
       </c>
       <c r="I75" t="n">
-        <v>2.131002</v>
+        <v>1.850693</v>
       </c>
       <c r="J75" t="n">
         <v>2.882893</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>8.899274</v>
+        <v>9.728630000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>10.436902</v>
+        <v>11.158928</v>
       </c>
       <c r="G76" t="n">
-        <v>9.57701</v>
+        <v>9.792424</v>
       </c>
       <c r="H76" t="n">
-        <v>7.7872</v>
+        <v>7.582943</v>
       </c>
       <c r="I76" t="n">
-        <v>6.966278</v>
+        <v>6.400576</v>
       </c>
       <c r="J76" t="n">
         <v>8.998787999999999</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.674763</v>
+        <v>3.567921</v>
       </c>
       <c r="F77" t="n">
-        <v>4.256084</v>
+        <v>4.217082</v>
       </c>
       <c r="G77" t="n">
-        <v>4.444168</v>
+        <v>4.435087</v>
       </c>
       <c r="H77" t="n">
-        <v>3.752613</v>
+        <v>3.7134</v>
       </c>
       <c r="I77" t="n">
-        <v>3.057206</v>
+        <v>2.939336</v>
       </c>
       <c r="J77" t="n">
         <v>3.292922</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>49.22656</v>
+        <v>55.609669</v>
       </c>
       <c r="F78" t="n">
-        <v>49.583867</v>
+        <v>54.329624</v>
       </c>
       <c r="G78" t="n">
-        <v>45.545897</v>
+        <v>48.498071</v>
       </c>
       <c r="H78" t="n">
-        <v>35.854124</v>
+        <v>37.72493</v>
       </c>
       <c r="I78" t="n">
-        <v>27.308165</v>
+        <v>28.725608</v>
       </c>
       <c r="J78" t="n">
         <v>19.691761</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7.027621</v>
+        <v>5.573256</v>
       </c>
       <c r="F79" t="n">
-        <v>7.568391</v>
+        <v>6.391794</v>
       </c>
       <c r="G79" t="n">
-        <v>7.900438</v>
+        <v>7.180306</v>
       </c>
       <c r="H79" t="n">
-        <v>7.497454</v>
+        <v>7.069506</v>
       </c>
       <c r="I79" t="n">
-        <v>6.774762</v>
+        <v>6.485846</v>
       </c>
       <c r="J79" t="n">
         <v>6.610336</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.514836</v>
+        <v>6.219691</v>
       </c>
       <c r="F80" t="n">
-        <v>7.810065</v>
+        <v>6.795284</v>
       </c>
       <c r="G80" t="n">
-        <v>8.809125999999999</v>
+        <v>7.092969</v>
       </c>
       <c r="H80" t="n">
-        <v>9.335592999999999</v>
+        <v>7.093076</v>
       </c>
       <c r="I80" t="n">
-        <v>11.224561</v>
+        <v>8.347757</v>
       </c>
       <c r="J80" t="n">
         <v>21.463675</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>8.190193000000001</v>
+        <v>5.632574</v>
       </c>
       <c r="F81" t="n">
-        <v>7.893842</v>
+        <v>5.675649</v>
       </c>
       <c r="G81" t="n">
-        <v>7.296858</v>
+        <v>5.622735</v>
       </c>
       <c r="H81" t="n">
-        <v>6.863426</v>
+        <v>5.500202</v>
       </c>
       <c r="I81" t="n">
-        <v>7.107064</v>
+        <v>5.769662</v>
       </c>
       <c r="J81" t="n">
         <v>10.867119</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>16.304851</v>
+        <v>18.108573</v>
       </c>
       <c r="F82" t="n">
-        <v>18.776006</v>
+        <v>20.358072</v>
       </c>
       <c r="G82" t="n">
-        <v>19.376173</v>
+        <v>20.616297</v>
       </c>
       <c r="H82" t="n">
-        <v>16.445211</v>
+        <v>17.53493</v>
       </c>
       <c r="I82" t="n">
-        <v>12.505906</v>
+        <v>13.689018</v>
       </c>
       <c r="J82" t="n">
         <v>6.378589</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>45.666419</v>
+        <v>41.222147</v>
       </c>
       <c r="F83" t="n">
-        <v>55.382986</v>
+        <v>52.996519</v>
       </c>
       <c r="G83" t="n">
-        <v>64.774098</v>
+        <v>64.713301</v>
       </c>
       <c r="H83" t="n">
-        <v>62.345803</v>
+        <v>63.901573</v>
       </c>
       <c r="I83" t="n">
-        <v>51.928832</v>
+        <v>54.79528</v>
       </c>
       <c r="J83" t="n">
         <v>32.908054</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>20.694677</v>
+        <v>20.508754</v>
       </c>
       <c r="F86" t="n">
-        <v>23.076965</v>
+        <v>22.926308</v>
       </c>
       <c r="G86" t="n">
-        <v>23.547851</v>
+        <v>23.424499</v>
       </c>
       <c r="H86" t="n">
-        <v>20.970871</v>
+        <v>20.894552</v>
       </c>
       <c r="I86" t="n">
-        <v>16.718045</v>
+        <v>16.686895</v>
       </c>
       <c r="J86" t="n">
         <v>13.672147</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.309196</v>
+        <v>1.323918</v>
       </c>
       <c r="F87" t="n">
-        <v>1.480857</v>
+        <v>1.494459</v>
       </c>
       <c r="G87" t="n">
-        <v>1.433461</v>
+        <v>1.446903</v>
       </c>
       <c r="H87" t="n">
-        <v>1.227497</v>
+        <v>1.236605</v>
       </c>
       <c r="I87" t="n">
-        <v>0.962573</v>
+        <v>0.966379</v>
       </c>
       <c r="J87" t="n">
         <v>0.78884</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>10.205471</v>
+        <v>10.7127</v>
       </c>
       <c r="F88" t="n">
-        <v>15.074184</v>
+        <v>15.31671</v>
       </c>
       <c r="G88" t="n">
-        <v>19.205943</v>
+        <v>19.293644</v>
       </c>
       <c r="H88" t="n">
-        <v>19.117118</v>
+        <v>19.137815</v>
       </c>
       <c r="I88" t="n">
-        <v>15.7734</v>
+        <v>15.776962</v>
       </c>
       <c r="J88" t="n">
         <v>12.786663</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.124498</v>
+        <v>2.211836</v>
       </c>
       <c r="F89" t="n">
-        <v>2.609072</v>
+        <v>2.662714</v>
       </c>
       <c r="G89" t="n">
-        <v>2.66895</v>
+        <v>2.705245</v>
       </c>
       <c r="H89" t="n">
-        <v>2.331802</v>
+        <v>2.351272</v>
       </c>
       <c r="I89" t="n">
-        <v>1.814485</v>
+        <v>1.821576</v>
       </c>
       <c r="J89" t="n">
         <v>1.451445</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15.36008</v>
+        <v>15.297446</v>
       </c>
       <c r="F90" t="n">
-        <v>18.650355</v>
+        <v>18.560804</v>
       </c>
       <c r="G90" t="n">
-        <v>18.394512</v>
+        <v>18.331492</v>
       </c>
       <c r="H90" t="n">
-        <v>15.251114</v>
+        <v>15.223335</v>
       </c>
       <c r="I90" t="n">
-        <v>11.268653</v>
+        <v>11.261129</v>
       </c>
       <c r="J90" t="n">
         <v>8.606764999999999</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5.646271</v>
+        <v>5.595942</v>
       </c>
       <c r="F91" t="n">
-        <v>6.395038</v>
+        <v>6.352537</v>
       </c>
       <c r="G91" t="n">
-        <v>6.400431</v>
+        <v>6.367928</v>
       </c>
       <c r="H91" t="n">
-        <v>5.679753</v>
+        <v>5.65961</v>
       </c>
       <c r="I91" t="n">
-        <v>4.572227</v>
+        <v>4.563628</v>
       </c>
       <c r="J91" t="n">
         <v>3.796926</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4.75695</v>
+        <v>4.686925</v>
       </c>
       <c r="F92" t="n">
-        <v>5.212403</v>
+        <v>5.160106</v>
       </c>
       <c r="G92" t="n">
-        <v>4.855131</v>
+        <v>4.82174</v>
       </c>
       <c r="H92" t="n">
-        <v>4.079022</v>
+        <v>4.061401</v>
       </c>
       <c r="I92" t="n">
-        <v>3.166273</v>
+        <v>3.159579</v>
       </c>
       <c r="J92" t="n">
         <v>2.57028</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.386201</v>
+        <v>0.388038</v>
       </c>
       <c r="F93" t="n">
-        <v>0.436969</v>
+        <v>0.438398</v>
       </c>
       <c r="G93" t="n">
-        <v>0.403901</v>
+        <v>0.405808</v>
       </c>
       <c r="H93" t="n">
-        <v>0.313626</v>
+        <v>0.315309</v>
       </c>
       <c r="I93" t="n">
-        <v>0.219076</v>
+        <v>0.219908</v>
       </c>
       <c r="J93" t="n">
         <v>0.160925</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>50.409685</v>
+        <v>51.275632</v>
       </c>
       <c r="F94" t="n">
-        <v>52.627288</v>
+        <v>53.391981</v>
       </c>
       <c r="G94" t="n">
-        <v>50.698835</v>
+        <v>51.298409</v>
       </c>
       <c r="H94" t="n">
-        <v>43.044705</v>
+        <v>43.389137</v>
       </c>
       <c r="I94" t="n">
-        <v>32.956058</v>
+        <v>33.084376</v>
       </c>
       <c r="J94" t="n">
         <v>25.883218</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>70.04775100000001</v>
+        <v>68.785481</v>
       </c>
       <c r="F95" t="n">
-        <v>69.960961</v>
+        <v>69.170543</v>
       </c>
       <c r="G95" t="n">
-        <v>62.709303</v>
+        <v>62.237922</v>
       </c>
       <c r="H95" t="n">
-        <v>50.535744</v>
+        <v>50.308954</v>
       </c>
       <c r="I95" t="n">
-        <v>37.305954</v>
+        <v>37.229447</v>
       </c>
       <c r="J95" t="n">
         <v>28.876938</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5.702176</v>
+        <v>5.799603</v>
       </c>
       <c r="F96" t="n">
-        <v>7.745332</v>
+        <v>7.778002</v>
       </c>
       <c r="G96" t="n">
-        <v>9.58544</v>
+        <v>9.574472</v>
       </c>
       <c r="H96" t="n">
-        <v>9.482260999999999</v>
+        <v>9.463479</v>
       </c>
       <c r="I96" t="n">
-        <v>7.822805</v>
+        <v>7.813541</v>
       </c>
       <c r="J96" t="n">
         <v>6.318312</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.740428</v>
+        <v>1.797108</v>
       </c>
       <c r="F97" t="n">
-        <v>2.725525</v>
+        <v>2.742385</v>
       </c>
       <c r="G97" t="n">
-        <v>3.588681</v>
+        <v>3.584377</v>
       </c>
       <c r="H97" t="n">
-        <v>3.637751</v>
+        <v>3.629795</v>
       </c>
       <c r="I97" t="n">
-        <v>3.031666</v>
+        <v>3.027796</v>
       </c>
       <c r="J97" t="n">
         <v>2.474809</v>
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10.33394</v>
+        <v>10.334889</v>
       </c>
       <c r="F98" t="n">
-        <v>13.562742</v>
+        <v>13.563144</v>
       </c>
       <c r="G98" t="n">
-        <v>16.614511</v>
+        <v>16.614499</v>
       </c>
       <c r="H98" t="n">
-        <v>17.980942</v>
+        <v>17.980607</v>
       </c>
       <c r="I98" t="n">
-        <v>16.203888</v>
+        <v>16.2034</v>
       </c>
       <c r="J98" t="n">
-        <v>13.67075</v>
+        <v>13.670233</v>
       </c>
       <c r="K98" t="n">
-        <v>10.709549</v>
+        <v>10.709083</v>
       </c>
       <c r="L98" t="n">
-        <v>8.477922</v>
+        <v>8.477515</v>
       </c>
       <c r="M98" t="n">
-        <v>6.818156</v>
+        <v>6.817804</v>
       </c>
       <c r="N98" t="n">
-        <v>5.57896</v>
+        <v>5.578654</v>
       </c>
       <c r="O98" t="n">
-        <v>4.502505</v>
+        <v>4.502245</v>
       </c>
       <c r="P98" t="n">
-        <v>3.905369</v>
+        <v>3.905133</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.340556</v>
+        <v>3.340348</v>
       </c>
       <c r="R98" t="n">
-        <v>3.078574</v>
+        <v>3.078379</v>
       </c>
       <c r="S98" t="n">
-        <v>2.599548</v>
+        <v>2.599383</v>
       </c>
       <c r="T98" t="n">
-        <v>1.603446</v>
+        <v>1.603345</v>
       </c>
       <c r="U98" t="n">
-        <v>0.610312</v>
+        <v>0.610274</v>
       </c>
       <c r="V98" t="n">
-        <v>-0.277417</v>
+        <v>-0.277401</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>13.112558</v>
+        <v>13.114277</v>
       </c>
       <c r="F99" t="n">
-        <v>11.607753</v>
+        <v>11.609384</v>
       </c>
       <c r="G99" t="n">
-        <v>9.24784</v>
+        <v>9.249675999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>7.252071</v>
+        <v>7.253993</v>
       </c>
       <c r="I99" t="n">
-        <v>5.287219</v>
+        <v>5.28892</v>
       </c>
       <c r="J99" t="n">
-        <v>3.940407</v>
+        <v>3.941838</v>
       </c>
       <c r="K99" t="n">
-        <v>2.886045</v>
+        <v>2.887175</v>
       </c>
       <c r="L99" t="n">
-        <v>2.21796</v>
+        <v>2.218873</v>
       </c>
       <c r="M99" t="n">
-        <v>1.770487</v>
+        <v>1.771244</v>
       </c>
       <c r="N99" t="n">
-        <v>1.453802</v>
+        <v>1.454443</v>
       </c>
       <c r="O99" t="n">
-        <v>1.183757</v>
+        <v>1.184294</v>
       </c>
       <c r="P99" t="n">
-        <v>1.037516</v>
+        <v>1.037997</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.897847</v>
+        <v>0.898267</v>
       </c>
       <c r="R99" t="n">
-        <v>0.839735</v>
+        <v>0.840128</v>
       </c>
       <c r="S99" t="n">
-        <v>0.720753</v>
+        <v>0.721085</v>
       </c>
       <c r="T99" t="n">
-        <v>0.450825</v>
+        <v>0.451026</v>
       </c>
       <c r="U99" t="n">
-        <v>0.173737</v>
+        <v>0.17381</v>
       </c>
       <c r="V99" t="n">
-        <v>-0.079706</v>
+        <v>-0.079737</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9.822971000000001</v>
+        <v>9.822962</v>
       </c>
       <c r="F100" t="n">
-        <v>13.394409</v>
+        <v>13.394114</v>
       </c>
       <c r="G100" t="n">
-        <v>16.164242</v>
+        <v>16.16366</v>
       </c>
       <c r="H100" t="n">
-        <v>17.214567</v>
+        <v>17.213773</v>
       </c>
       <c r="I100" t="n">
-        <v>15.392629</v>
+        <v>15.391802</v>
       </c>
       <c r="J100" t="n">
-        <v>13.017648</v>
+        <v>13.01687</v>
       </c>
       <c r="K100" t="n">
-        <v>10.275582</v>
+        <v>10.274916</v>
       </c>
       <c r="L100" t="n">
-        <v>8.250613</v>
+        <v>8.250038999999999</v>
       </c>
       <c r="M100" t="n">
-        <v>6.763769</v>
+        <v>6.763268</v>
       </c>
       <c r="N100" t="n">
-        <v>5.655972</v>
+        <v>5.655529</v>
       </c>
       <c r="O100" t="n">
-        <v>4.675977</v>
+        <v>4.675592</v>
       </c>
       <c r="P100" t="n">
-        <v>4.149994</v>
+        <v>4.149638</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.627013</v>
+        <v>3.626693</v>
       </c>
       <c r="R100" t="n">
-        <v>3.417547</v>
+        <v>3.41724</v>
       </c>
       <c r="S100" t="n">
-        <v>2.948672</v>
+        <v>2.948406</v>
       </c>
       <c r="T100" t="n">
-        <v>1.852505</v>
+        <v>1.852341</v>
       </c>
       <c r="U100" t="n">
-        <v>0.719493</v>
+        <v>0.719431</v>
       </c>
       <c r="V100" t="n">
-        <v>-0.336279</v>
+        <v>-0.336252</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>9.181538</v>
+        <v>9.18196</v>
       </c>
       <c r="F101" t="n">
-        <v>10.272632</v>
+        <v>10.272892</v>
       </c>
       <c r="G101" t="n">
-        <v>10.31301</v>
+        <v>10.313199</v>
       </c>
       <c r="H101" t="n">
-        <v>9.577387999999999</v>
+        <v>9.577525</v>
       </c>
       <c r="I101" t="n">
-        <v>7.824872</v>
+        <v>7.824953</v>
       </c>
       <c r="J101" t="n">
-        <v>6.259538</v>
+        <v>6.259577</v>
       </c>
       <c r="K101" t="n">
-        <v>4.786818</v>
+        <v>4.78683</v>
       </c>
       <c r="L101" t="n">
-        <v>3.780021</v>
+        <v>3.780017</v>
       </c>
       <c r="M101" t="n">
-        <v>3.075466</v>
+        <v>3.075452</v>
       </c>
       <c r="N101" t="n">
-        <v>2.559166</v>
+        <v>2.559147</v>
       </c>
       <c r="O101" t="n">
-        <v>2.104501</v>
+        <v>2.104481</v>
       </c>
       <c r="P101" t="n">
-        <v>1.855081</v>
+        <v>1.855061</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.609375</v>
+        <v>1.609356</v>
       </c>
       <c r="R101" t="n">
-        <v>1.505799</v>
+        <v>1.505779</v>
       </c>
       <c r="S101" t="n">
-        <v>1.295351</v>
+        <v>1.295333</v>
       </c>
       <c r="T101" t="n">
-        <v>0.8144709999999999</v>
+        <v>0.814459</v>
       </c>
       <c r="U101" t="n">
-        <v>0.316082</v>
+        <v>0.316077</v>
       </c>
       <c r="V101" t="n">
-        <v>-0.146546</v>
+        <v>-0.146544</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>116.477841</v>
+        <v>116.475568</v>
       </c>
       <c r="F102" t="n">
-        <v>114.429278</v>
+        <v>114.428572</v>
       </c>
       <c r="G102" t="n">
-        <v>98.18191</v>
+        <v>98.182439</v>
       </c>
       <c r="H102" t="n">
-        <v>79.648363</v>
+        <v>79.649844</v>
       </c>
       <c r="I102" t="n">
-        <v>58.550805</v>
+        <v>58.552636</v>
       </c>
       <c r="J102" t="n">
-        <v>43.460979</v>
+        <v>43.462787</v>
       </c>
       <c r="K102" t="n">
-        <v>31.587365</v>
+        <v>31.588917</v>
       </c>
       <c r="L102" t="n">
-        <v>24.116365</v>
+        <v>24.117672</v>
       </c>
       <c r="M102" t="n">
-        <v>19.223467</v>
+        <v>19.224565</v>
       </c>
       <c r="N102" t="n">
-        <v>15.845575</v>
+        <v>15.846505</v>
       </c>
       <c r="O102" t="n">
-        <v>13.01323</v>
+        <v>13.014002</v>
       </c>
       <c r="P102" t="n">
-        <v>11.518438</v>
+        <v>11.519125</v>
       </c>
       <c r="Q102" t="n">
-        <v>10.0653</v>
+        <v>10.065898</v>
       </c>
       <c r="R102" t="n">
-        <v>9.500135</v>
+        <v>9.500693</v>
       </c>
       <c r="S102" t="n">
-        <v>8.217591000000001</v>
+        <v>8.218064999999999</v>
       </c>
       <c r="T102" t="n">
-        <v>5.152734</v>
+        <v>5.153025</v>
       </c>
       <c r="U102" t="n">
-        <v>1.991501</v>
+        <v>1.991609</v>
       </c>
       <c r="V102" t="n">
-        <v>-0.92323</v>
+        <v>-0.923275</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>157.992584</v>
+        <v>157.999657</v>
       </c>
       <c r="F103" t="n">
-        <v>214.612049</v>
+        <v>214.611871</v>
       </c>
       <c r="G103" t="n">
-        <v>265.739665</v>
+        <v>265.733251</v>
       </c>
       <c r="H103" t="n">
-        <v>286.00093</v>
+        <v>285.990033</v>
       </c>
       <c r="I103" t="n">
-        <v>253.153552</v>
+        <v>253.141616</v>
       </c>
       <c r="J103" t="n">
-        <v>208.756384</v>
+        <v>208.745248</v>
       </c>
       <c r="K103" t="n">
-        <v>158.743011</v>
+        <v>158.733808</v>
       </c>
       <c r="L103" t="n">
-        <v>121.734858</v>
+        <v>121.727356</v>
       </c>
       <c r="M103" t="n">
-        <v>94.911411</v>
+        <v>94.905259</v>
       </c>
       <c r="N103" t="n">
-        <v>75.68128400000001</v>
+        <v>75.676158</v>
       </c>
       <c r="O103" t="n">
-        <v>59.842491</v>
+        <v>59.838274</v>
       </c>
       <c r="P103" t="n">
-        <v>51.015239</v>
+        <v>51.011531</v>
       </c>
       <c r="Q103" t="n">
-        <v>42.902419</v>
+        <v>42.899241</v>
       </c>
       <c r="R103" t="n">
-        <v>38.840928</v>
+        <v>38.838035</v>
       </c>
       <c r="S103" t="n">
-        <v>32.234013</v>
+        <v>32.231635</v>
       </c>
       <c r="T103" t="n">
-        <v>19.565189</v>
+        <v>19.563781</v>
       </c>
       <c r="U103" t="n">
-        <v>7.36774</v>
+        <v>7.367234</v>
       </c>
       <c r="V103" t="n">
-        <v>-3.303333</v>
+        <v>-3.303124</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>27.335853</v>
+        <v>27.335055</v>
       </c>
       <c r="F104" t="n">
-        <v>26.856689</v>
+        <v>26.856252</v>
       </c>
       <c r="G104" t="n">
-        <v>23.627617</v>
+        <v>23.627356</v>
       </c>
       <c r="H104" t="n">
-        <v>18.891765</v>
+        <v>18.891719</v>
       </c>
       <c r="I104" t="n">
-        <v>13.389678</v>
+        <v>13.389786</v>
       </c>
       <c r="J104" t="n">
-        <v>9.499984</v>
+        <v>9.500163000000001</v>
       </c>
       <c r="K104" t="n">
-        <v>6.625542</v>
+        <v>6.625725</v>
       </c>
       <c r="L104" t="n">
-        <v>4.900047</v>
+        <v>4.900209</v>
       </c>
       <c r="M104" t="n">
-        <v>3.800498</v>
+        <v>3.800635</v>
       </c>
       <c r="N104" t="n">
-        <v>3.052313</v>
+        <v>3.052427</v>
       </c>
       <c r="O104" t="n">
-        <v>2.435725</v>
+        <v>2.435817</v>
       </c>
       <c r="P104" t="n">
-        <v>2.095742</v>
+        <v>2.095822</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.787541</v>
+        <v>1.787607</v>
       </c>
       <c r="R104" t="n">
-        <v>1.656425</v>
+        <v>1.656482</v>
       </c>
       <c r="S104" t="n">
-        <v>1.414546</v>
+        <v>1.41459</v>
       </c>
       <c r="T104" t="n">
-        <v>0.880687</v>
+        <v>0.8807120000000001</v>
       </c>
       <c r="U104" t="n">
-        <v>0.336715</v>
+        <v>0.336724</v>
       </c>
       <c r="V104" t="n">
-        <v>-0.152981</v>
+        <v>-0.152984</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>7.143144</v>
+        <v>7.143529</v>
       </c>
       <c r="F105" t="n">
-        <v>8.247289</v>
+        <v>8.247543</v>
       </c>
       <c r="G105" t="n">
-        <v>8.041941</v>
+        <v>8.042191000000001</v>
       </c>
       <c r="H105" t="n">
-        <v>7.326404</v>
+        <v>7.32665</v>
       </c>
       <c r="I105" t="n">
-        <v>5.986939</v>
+        <v>5.98714</v>
       </c>
       <c r="J105" t="n">
-        <v>4.900818</v>
+        <v>4.900966</v>
       </c>
       <c r="K105" t="n">
-        <v>3.875816</v>
+        <v>3.875914</v>
       </c>
       <c r="L105" t="n">
-        <v>3.167989</v>
+        <v>3.168051</v>
       </c>
       <c r="M105" t="n">
-        <v>2.648592</v>
+        <v>2.64863</v>
       </c>
       <c r="N105" t="n">
-        <v>2.249713</v>
+        <v>2.249736</v>
       </c>
       <c r="O105" t="n">
-        <v>1.879739</v>
+        <v>1.879753</v>
       </c>
       <c r="P105" t="n">
-        <v>1.685537</v>
+        <v>1.685544</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.493607</v>
+        <v>1.493608</v>
       </c>
       <c r="R105" t="n">
-        <v>1.434704</v>
+        <v>1.434699</v>
       </c>
       <c r="S105" t="n">
-        <v>1.26738</v>
+        <v>1.267371</v>
       </c>
       <c r="T105" t="n">
-        <v>0.814966</v>
+        <v>0.814957</v>
       </c>
       <c r="U105" t="n">
-        <v>0.32188</v>
+        <v>0.321876</v>
       </c>
       <c r="V105" t="n">
-        <v>-0.151706</v>
+        <v>-0.151704</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>150.500999</v>
+        <v>150.495742</v>
       </c>
       <c r="F106" t="n">
-        <v>131.904768</v>
+        <v>131.903312</v>
       </c>
       <c r="G106" t="n">
-        <v>98.557885</v>
+        <v>98.559089</v>
       </c>
       <c r="H106" t="n">
-        <v>71.854125</v>
+        <v>71.85696799999999</v>
       </c>
       <c r="I106" t="n">
-        <v>48.777835</v>
+        <v>48.781118</v>
       </c>
       <c r="J106" t="n">
-        <v>34.193207</v>
+        <v>34.196319</v>
       </c>
       <c r="K106" t="n">
-        <v>23.843112</v>
+        <v>23.845712</v>
       </c>
       <c r="L106" t="n">
-        <v>17.660445</v>
+        <v>17.662588</v>
       </c>
       <c r="M106" t="n">
-        <v>13.647732</v>
+        <v>13.649516</v>
       </c>
       <c r="N106" t="n">
-        <v>10.877013</v>
+        <v>10.878521</v>
       </c>
       <c r="O106" t="n">
-        <v>8.617578</v>
+        <v>8.618834</v>
       </c>
       <c r="P106" t="n">
-        <v>7.384876</v>
+        <v>7.385989</v>
       </c>
       <c r="Q106" t="n">
-        <v>6.290196</v>
+        <v>6.291154</v>
       </c>
       <c r="R106" t="n">
-        <v>5.826313</v>
+        <v>5.827194</v>
       </c>
       <c r="S106" t="n">
-        <v>4.962111</v>
+        <v>4.962846</v>
       </c>
       <c r="T106" t="n">
-        <v>3.058724</v>
+        <v>3.059168</v>
       </c>
       <c r="U106" t="n">
-        <v>1.153192</v>
+        <v>1.153355</v>
       </c>
       <c r="V106" t="n">
-        <v>-0.520002</v>
+        <v>-0.5200709999999999</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.04529</v>
+        <v>0.045568</v>
       </c>
       <c r="F107" t="n">
-        <v>0.043915</v>
+        <v>0.044147</v>
       </c>
       <c r="G107" t="n">
-        <v>0.044496</v>
+        <v>0.044725</v>
       </c>
       <c r="H107" t="n">
-        <v>0.043188</v>
+        <v>0.04341</v>
       </c>
       <c r="I107" t="n">
-        <v>0.036694</v>
+        <v>0.036885</v>
       </c>
       <c r="J107" t="n">
-        <v>0.030216</v>
+        <v>0.030377</v>
       </c>
       <c r="K107" t="n">
-        <v>0.023651</v>
+        <v>0.023781</v>
       </c>
       <c r="L107" t="n">
-        <v>0.019098</v>
+        <v>0.019206</v>
       </c>
       <c r="M107" t="n">
-        <v>0.015922</v>
+        <v>0.016014</v>
       </c>
       <c r="N107" t="n">
-        <v>0.013658</v>
+        <v>0.013738</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0116</v>
+        <v>0.011669</v>
       </c>
       <c r="P107" t="n">
-        <v>0.010582</v>
+        <v>0.010645</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.009508000000000001</v>
+        <v>0.009563</v>
       </c>
       <c r="R107" t="n">
-        <v>0.009211</v>
+        <v>0.009264</v>
       </c>
       <c r="S107" t="n">
-        <v>0.008178</v>
+        <v>0.008222999999999999</v>
       </c>
       <c r="T107" t="n">
-        <v>0.005288</v>
+        <v>0.005315</v>
       </c>
       <c r="U107" t="n">
-        <v>0.002105</v>
+        <v>0.002115</v>
       </c>
       <c r="V107" t="n">
-        <v>-0.000998</v>
+        <v>-0.001002</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>13.756788</v>
+        <v>13.760479</v>
       </c>
       <c r="F108" t="n">
-        <v>14.674374</v>
+        <v>14.677133</v>
       </c>
       <c r="G108" t="n">
-        <v>14.72865</v>
+        <v>14.73113</v>
       </c>
       <c r="H108" t="n">
-        <v>13.762282</v>
+        <v>13.764506</v>
       </c>
       <c r="I108" t="n">
-        <v>11.263657</v>
+        <v>11.265432</v>
       </c>
       <c r="J108" t="n">
-        <v>8.973579000000001</v>
+        <v>8.974973</v>
       </c>
       <c r="K108" t="n">
-        <v>6.813417</v>
+        <v>6.814468</v>
       </c>
       <c r="L108" t="n">
-        <v>5.327208</v>
+        <v>5.328031</v>
       </c>
       <c r="M108" t="n">
-        <v>4.288617</v>
+        <v>4.289284</v>
       </c>
       <c r="N108" t="n">
-        <v>3.540715</v>
+        <v>3.541272</v>
       </c>
       <c r="O108" t="n">
-        <v>2.901302</v>
+        <v>2.901764</v>
       </c>
       <c r="P108" t="n">
-        <v>2.557119</v>
+        <v>2.55753</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.222503</v>
+        <v>2.222863</v>
       </c>
       <c r="R108" t="n">
-        <v>2.081409</v>
+        <v>2.081747</v>
       </c>
       <c r="S108" t="n">
-        <v>1.783028</v>
+        <v>1.783318</v>
       </c>
       <c r="T108" t="n">
-        <v>1.112306</v>
+        <v>1.112485</v>
       </c>
       <c r="U108" t="n">
-        <v>0.429477</v>
+        <v>0.429543</v>
       </c>
       <c r="V108" t="n">
-        <v>-0.19846</v>
+        <v>-0.198488</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>69.88784800000001</v>
+        <v>69.88198300000001</v>
       </c>
       <c r="F109" t="n">
-        <v>71.61145500000001</v>
+        <v>71.60724</v>
       </c>
       <c r="G109" t="n">
-        <v>57.571359</v>
+        <v>57.568241</v>
       </c>
       <c r="H109" t="n">
-        <v>40.411261</v>
+        <v>40.409289</v>
       </c>
       <c r="I109" t="n">
-        <v>24.793567</v>
+        <v>24.792594</v>
       </c>
       <c r="J109" t="n">
-        <v>15.639521</v>
+        <v>15.639098</v>
       </c>
       <c r="K109" t="n">
-        <v>10.016941</v>
+        <v>10.01679</v>
       </c>
       <c r="L109" t="n">
-        <v>6.992369</v>
+        <v>6.99233</v>
       </c>
       <c r="M109" t="n">
-        <v>5.227017</v>
+        <v>5.227022</v>
       </c>
       <c r="N109" t="n">
-        <v>4.108015</v>
+        <v>4.108036</v>
       </c>
       <c r="O109" t="n">
-        <v>3.242007</v>
+        <v>3.242033</v>
       </c>
       <c r="P109" t="n">
-        <v>2.774467</v>
+        <v>2.774494</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.358325</v>
+        <v>2.358349</v>
       </c>
       <c r="R109" t="n">
-        <v>2.18155</v>
+        <v>2.181571</v>
       </c>
       <c r="S109" t="n">
-        <v>1.861867</v>
+        <v>1.861882</v>
       </c>
       <c r="T109" t="n">
-        <v>1.159523</v>
+        <v>1.159531</v>
       </c>
       <c r="U109" t="n">
-        <v>0.444729</v>
+        <v>0.444731</v>
       </c>
       <c r="V109" t="n">
-        <v>-0.203469</v>
+        <v>-0.20347</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>11.545612</v>
+        <v>11.545687</v>
       </c>
       <c r="F110" t="n">
-        <v>11.118703</v>
+        <v>11.118907</v>
       </c>
       <c r="G110" t="n">
-        <v>9.422418</v>
+        <v>9.422767</v>
       </c>
       <c r="H110" t="n">
-        <v>7.740673</v>
+        <v>7.741106</v>
       </c>
       <c r="I110" t="n">
-        <v>5.896823</v>
+        <v>5.897228</v>
       </c>
       <c r="J110" t="n">
-        <v>4.582363</v>
+        <v>4.582707</v>
       </c>
       <c r="K110" t="n">
-        <v>3.498891</v>
+        <v>3.499158</v>
       </c>
       <c r="L110" t="n">
-        <v>2.796621</v>
+        <v>2.796832</v>
       </c>
       <c r="M110" t="n">
-        <v>2.312186</v>
+        <v>2.312356</v>
       </c>
       <c r="N110" t="n">
-        <v>1.954218</v>
+        <v>1.954359</v>
       </c>
       <c r="O110" t="n">
-        <v>1.627589</v>
+        <v>1.627706</v>
       </c>
       <c r="P110" t="n">
-        <v>1.45365</v>
+        <v>1.453755</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.279959</v>
+        <v>1.280051</v>
       </c>
       <c r="R110" t="n">
-        <v>1.217627</v>
+        <v>1.217712</v>
       </c>
       <c r="S110" t="n">
-        <v>1.062924</v>
+        <v>1.062995</v>
       </c>
       <c r="T110" t="n">
-        <v>0.676518</v>
+        <v>0.6765600000000001</v>
       </c>
       <c r="U110" t="n">
-        <v>0.265908</v>
+        <v>0.265923</v>
       </c>
       <c r="V110" t="n">
-        <v>-0.124793</v>
+        <v>-0.124799</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>110.938698</v>
+        <v>110.935253</v>
       </c>
       <c r="F111" t="n">
-        <v>109.119659</v>
+        <v>109.117905</v>
       </c>
       <c r="G111" t="n">
-        <v>97.626284</v>
+        <v>97.625244</v>
       </c>
       <c r="H111" t="n">
-        <v>83.007375</v>
+        <v>83.006838</v>
       </c>
       <c r="I111" t="n">
-        <v>63.042549</v>
+        <v>63.04239</v>
       </c>
       <c r="J111" t="n">
-        <v>47.800622</v>
+        <v>47.800642</v>
       </c>
       <c r="K111" t="n">
-        <v>35.364292</v>
+        <v>35.364341</v>
       </c>
       <c r="L111" t="n">
         <v>27.51782</v>
       </c>
       <c r="M111" t="n">
-        <v>22.180188</v>
+        <v>22.180135</v>
       </c>
       <c r="N111" t="n">
-        <v>18.311749</v>
+        <v>18.31166</v>
       </c>
       <c r="O111" t="n">
-        <v>14.92046</v>
+        <v>14.920354</v>
       </c>
       <c r="P111" t="n">
-        <v>13.095632</v>
+        <v>13.095508</v>
       </c>
       <c r="Q111" t="n">
-        <v>11.416682</v>
+        <v>11.416537</v>
       </c>
       <c r="R111" t="n">
-        <v>10.853462</v>
+        <v>10.853278</v>
       </c>
       <c r="S111" t="n">
-        <v>9.548437</v>
+        <v>9.54823</v>
       </c>
       <c r="T111" t="n">
-        <v>6.100355</v>
+        <v>6.100202</v>
       </c>
       <c r="U111" t="n">
-        <v>2.377105</v>
+        <v>2.377043</v>
       </c>
       <c r="V111" t="n">
-        <v>-1.101297</v>
+        <v>-1.101268</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>90.15180599999999</v>
+        <v>90.154859</v>
       </c>
       <c r="F112" t="n">
-        <v>88.02258399999999</v>
+        <v>88.025882</v>
       </c>
       <c r="G112" t="n">
-        <v>74.331457</v>
+        <v>74.33581599999999</v>
       </c>
       <c r="H112" t="n">
-        <v>59.712663</v>
+        <v>59.717738</v>
       </c>
       <c r="I112" t="n">
-        <v>43.684795</v>
+        <v>43.689604</v>
       </c>
       <c r="J112" t="n">
-        <v>32.437985</v>
+        <v>32.442202</v>
       </c>
       <c r="K112" t="n">
-        <v>23.705073</v>
+        <v>23.70849</v>
       </c>
       <c r="L112" t="n">
-        <v>18.268607</v>
+        <v>18.271403</v>
       </c>
       <c r="M112" t="n">
-        <v>14.705134</v>
+        <v>14.707459</v>
       </c>
       <c r="N112" t="n">
-        <v>12.20356</v>
+        <v>12.205528</v>
       </c>
       <c r="O112" t="n">
-        <v>10.05498</v>
+        <v>10.056625</v>
       </c>
       <c r="P112" t="n">
-        <v>8.911638</v>
+        <v>8.913112999999999</v>
       </c>
       <c r="Q112" t="n">
-        <v>7.79076</v>
+        <v>7.792055</v>
       </c>
       <c r="R112" t="n">
-        <v>7.35306</v>
+        <v>7.354278</v>
       </c>
       <c r="S112" t="n">
-        <v>6.368422</v>
+        <v>6.369459</v>
       </c>
       <c r="T112" t="n">
-        <v>4.027755</v>
+        <v>4.028387</v>
       </c>
       <c r="U112" t="n">
-        <v>1.575882</v>
+        <v>1.576113</v>
       </c>
       <c r="V112" t="n">
-        <v>-0.738723</v>
+        <v>-0.73882</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15.0662</v>
+        <v>15.382242</v>
       </c>
       <c r="F113" t="n">
-        <v>16.282225</v>
+        <v>16.587894</v>
       </c>
       <c r="G113" t="n">
-        <v>12.84022</v>
+        <v>12.933567</v>
       </c>
       <c r="H113" t="n">
-        <v>10.130536</v>
+        <v>10.062318</v>
       </c>
       <c r="I113" t="n">
-        <v>8.114341</v>
+        <v>7.866042</v>
       </c>
       <c r="J113" t="n">
         <v>9.582744</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2.773022</v>
+        <v>2.479069</v>
       </c>
       <c r="F114" t="n">
-        <v>3.864121</v>
+        <v>3.59933</v>
       </c>
       <c r="G114" t="n">
-        <v>4.120528</v>
+        <v>3.982598</v>
       </c>
       <c r="H114" t="n">
-        <v>4.010084</v>
+        <v>3.936484</v>
       </c>
       <c r="I114" t="n">
-        <v>3.45545</v>
+        <v>3.413608</v>
       </c>
       <c r="J114" t="n">
         <v>3.037277</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>59.958335</v>
+        <v>59.936246</v>
       </c>
       <c r="F115" t="n">
-        <v>74.224735</v>
+        <v>74.18385600000001</v>
       </c>
       <c r="G115" t="n">
-        <v>71.48960700000001</v>
+        <v>71.53419</v>
       </c>
       <c r="H115" t="n">
-        <v>64.698026</v>
+        <v>64.839844</v>
       </c>
       <c r="I115" t="n">
-        <v>54.11772</v>
+        <v>54.407861</v>
       </c>
       <c r="J115" t="n">
         <v>44.379329</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>18.810305</v>
+        <v>16.87981</v>
       </c>
       <c r="F116" t="n">
-        <v>22.295734</v>
+        <v>20.682501</v>
       </c>
       <c r="G116" t="n">
-        <v>21.653686</v>
+        <v>20.342111</v>
       </c>
       <c r="H116" t="n">
-        <v>19.547809</v>
+        <v>18.512343</v>
       </c>
       <c r="I116" t="n">
-        <v>16.308702</v>
+        <v>15.533583</v>
       </c>
       <c r="J116" t="n">
-        <v>13.700864</v>
+        <v>13.105079</v>
       </c>
       <c r="K116" t="n">
-        <v>11.294699</v>
+        <v>10.837926</v>
       </c>
       <c r="L116" t="n">
-        <v>9.405063999999999</v>
+        <v>9.048634</v>
       </c>
       <c r="M116" t="n">
-        <v>8.019646</v>
+        <v>7.733431</v>
       </c>
       <c r="N116" t="n">
-        <v>6.922027</v>
+        <v>6.68878</v>
       </c>
       <c r="O116" t="n">
-        <v>5.895717</v>
+        <v>5.708227</v>
       </c>
       <c r="P116" t="n">
-        <v>5.097988</v>
+        <v>4.945351</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.303488</v>
+        <v>4.183055</v>
       </c>
       <c r="R116" t="n">
-        <v>3.462347</v>
+        <v>3.372633</v>
       </c>
       <c r="S116" t="n">
-        <v>2.758804</v>
+        <v>2.693476</v>
       </c>
       <c r="T116" t="n">
-        <v>2.062067</v>
+        <v>2.018115</v>
       </c>
       <c r="U116" t="n">
-        <v>1.347612</v>
+        <v>1.322276</v>
       </c>
       <c r="V116" t="n">
-        <v>0.7577199999999999</v>
+        <v>0.7455850000000001</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5.004215</v>
+        <v>5.16839</v>
       </c>
       <c r="F117" t="n">
-        <v>4.069685</v>
+        <v>4.458904</v>
       </c>
       <c r="G117" t="n">
-        <v>3.284101</v>
+        <v>3.704564</v>
       </c>
       <c r="H117" t="n">
-        <v>2.634564</v>
+        <v>3.013215</v>
       </c>
       <c r="I117" t="n">
-        <v>2.019865</v>
+        <v>2.320107</v>
       </c>
       <c r="J117" t="n">
-        <v>1.58823</v>
+        <v>1.823023</v>
       </c>
       <c r="K117" t="n">
-        <v>1.23997</v>
+        <v>1.419204</v>
       </c>
       <c r="L117" t="n">
-        <v>0.983602</v>
+        <v>1.121523</v>
       </c>
       <c r="M117" t="n">
-        <v>0.804381</v>
+        <v>0.9127729999999999</v>
       </c>
       <c r="N117" t="n">
-        <v>0.669889</v>
+        <v>0.756008</v>
       </c>
       <c r="O117" t="n">
-        <v>0.551284</v>
+        <v>0.619041</v>
       </c>
       <c r="P117" t="n">
-        <v>0.459882</v>
+        <v>0.514266</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.372922</v>
+        <v>0.41568</v>
       </c>
       <c r="R117" t="n">
-        <v>0.287414</v>
+        <v>0.319439</v>
       </c>
       <c r="S117" t="n">
-        <v>0.219157</v>
+        <v>0.242758</v>
       </c>
       <c r="T117" t="n">
-        <v>0.15704</v>
+        <v>0.173151</v>
       </c>
       <c r="U117" t="n">
-        <v>0.098513</v>
+        <v>0.107939</v>
       </c>
       <c r="V117" t="n">
-        <v>0.052975</v>
+        <v>0.057565</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2.570385</v>
+        <v>2.908906</v>
       </c>
       <c r="F118" t="n">
-        <v>2.632444</v>
+        <v>2.910838</v>
       </c>
       <c r="G118" t="n">
-        <v>2.449082</v>
+        <v>2.671634</v>
       </c>
       <c r="H118" t="n">
-        <v>2.161899</v>
+        <v>2.334267</v>
       </c>
       <c r="I118" t="n">
-        <v>1.775235</v>
+        <v>1.901085</v>
       </c>
       <c r="J118" t="n">
-        <v>1.474923</v>
+        <v>1.568608</v>
       </c>
       <c r="K118" t="n">
-        <v>1.207545</v>
+        <v>1.276815</v>
       </c>
       <c r="L118" t="n">
-        <v>1.002453</v>
+        <v>1.054502</v>
       </c>
       <c r="M118" t="n">
-        <v>0.85587</v>
+        <v>0.896109</v>
       </c>
       <c r="N118" t="n">
-        <v>0.74091</v>
+        <v>0.772693</v>
       </c>
       <c r="O118" t="n">
-        <v>0.630456</v>
+        <v>0.655653</v>
       </c>
       <c r="P118" t="n">
-        <v>0.542766</v>
+        <v>0.563316</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.45394</v>
+        <v>0.470491</v>
       </c>
       <c r="R118" t="n">
-        <v>0.360437</v>
+        <v>0.373209</v>
       </c>
       <c r="S118" t="n">
-        <v>0.282714</v>
+        <v>0.29244</v>
       </c>
       <c r="T118" t="n">
-        <v>0.207783</v>
+        <v>0.21464</v>
       </c>
       <c r="U118" t="n">
-        <v>0.13338</v>
+        <v>0.137511</v>
       </c>
       <c r="V118" t="n">
-        <v>0.073445</v>
+        <v>0.075507</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2.823152</v>
+        <v>2.783523</v>
       </c>
       <c r="F119" t="n">
-        <v>2.540139</v>
+        <v>2.598793</v>
       </c>
       <c r="G119" t="n">
-        <v>2.018278</v>
+        <v>2.128136</v>
       </c>
       <c r="H119" t="n">
-        <v>1.592679</v>
+        <v>1.715553</v>
       </c>
       <c r="I119" t="n">
-        <v>1.224872</v>
+        <v>1.334596</v>
       </c>
       <c r="J119" t="n">
-        <v>0.98405</v>
+        <v>1.07667</v>
       </c>
       <c r="K119" t="n">
-        <v>0.796323</v>
+        <v>0.870906</v>
       </c>
       <c r="L119" t="n">
-        <v>0.660724</v>
+        <v>0.720574</v>
       </c>
       <c r="M119" t="n">
-        <v>0.566594</v>
+        <v>0.615507</v>
       </c>
       <c r="N119" t="n">
-        <v>0.493646</v>
+        <v>0.53413</v>
       </c>
       <c r="O119" t="n">
-        <v>0.422009</v>
+        <v>0.455236</v>
       </c>
       <c r="P119" t="n">
-        <v>0.364803</v>
+        <v>0.392504</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.306584</v>
+        <v>0.329079</v>
       </c>
       <c r="R119" t="n">
-        <v>0.244483</v>
+        <v>0.261819</v>
       </c>
       <c r="S119" t="n">
-        <v>0.192168</v>
+        <v>0.205285</v>
       </c>
       <c r="T119" t="n">
-        <v>0.141084</v>
+        <v>0.150251</v>
       </c>
       <c r="U119" t="n">
-        <v>0.090174</v>
+        <v>0.095642</v>
       </c>
       <c r="V119" t="n">
-        <v>0.049238</v>
+        <v>0.051936</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.573199</v>
+        <v>0.509229</v>
       </c>
       <c r="F120" t="n">
-        <v>0.687233</v>
+        <v>0.6333800000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>0.674319</v>
+        <v>0.6300789999999999</v>
       </c>
       <c r="H120" t="n">
-        <v>0.61611</v>
+        <v>0.580749</v>
       </c>
       <c r="I120" t="n">
-        <v>0.521089</v>
+        <v>0.494263</v>
       </c>
       <c r="J120" t="n">
-        <v>0.44443</v>
+        <v>0.423512</v>
       </c>
       <c r="K120" t="n">
-        <v>0.372415</v>
+        <v>0.356129</v>
       </c>
       <c r="L120" t="n">
-        <v>0.315664</v>
+        <v>0.302742</v>
       </c>
       <c r="M120" t="n">
-        <v>0.274368</v>
+        <v>0.263801</v>
       </c>
       <c r="N120" t="n">
-        <v>0.241632</v>
+        <v>0.232853</v>
       </c>
       <c r="O120" t="n">
-        <v>0.209716</v>
+        <v>0.20253</v>
       </c>
       <c r="P120" t="n">
-        <v>0.184635</v>
+        <v>0.178682</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.158663</v>
+        <v>0.153884</v>
       </c>
       <c r="R120" t="n">
-        <v>0.129965</v>
+        <v>0.126342</v>
       </c>
       <c r="S120" t="n">
-        <v>0.105437</v>
+        <v>0.102752</v>
       </c>
       <c r="T120" t="n">
-        <v>0.080155</v>
+        <v>0.078319</v>
       </c>
       <c r="U120" t="n">
-        <v>0.053161</v>
+        <v>0.052087</v>
       </c>
       <c r="V120" t="n">
-        <v>0.030228</v>
+        <v>0.029708</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>9.332554999999999</v>
+        <v>8.291024999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>8.144247999999999</v>
+        <v>7.50605</v>
       </c>
       <c r="G121" t="n">
-        <v>6.177149</v>
+        <v>5.771888</v>
       </c>
       <c r="H121" t="n">
-        <v>4.787358</v>
+        <v>4.512597</v>
       </c>
       <c r="I121" t="n">
-        <v>3.702063</v>
+        <v>3.511473</v>
       </c>
       <c r="J121" t="n">
-        <v>3.031427</v>
+        <v>2.888744</v>
       </c>
       <c r="K121" t="n">
-        <v>2.510467</v>
+        <v>2.400685</v>
       </c>
       <c r="L121" t="n">
-        <v>2.133825</v>
+        <v>2.046476</v>
       </c>
       <c r="M121" t="n">
-        <v>1.866271</v>
+        <v>1.794396</v>
       </c>
       <c r="N121" t="n">
-        <v>1.648134</v>
+        <v>1.588254</v>
       </c>
       <c r="O121" t="n">
-        <v>1.420396</v>
+        <v>1.371725</v>
       </c>
       <c r="P121" t="n">
-        <v>1.234397</v>
+        <v>1.194597</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.040936</v>
+        <v>1.009582</v>
       </c>
       <c r="R121" t="n">
-        <v>0.832761</v>
+        <v>0.809547</v>
       </c>
       <c r="S121" t="n">
-        <v>0.656998</v>
+        <v>0.6402679999999999</v>
       </c>
       <c r="T121" t="n">
-        <v>0.484799</v>
+        <v>0.473692</v>
       </c>
       <c r="U121" t="n">
-        <v>0.311929</v>
+        <v>0.305628</v>
       </c>
       <c r="V121" t="n">
-        <v>0.172033</v>
+        <v>0.169075</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>91.308665</v>
+        <v>93.881595</v>
       </c>
       <c r="F122" t="n">
-        <v>110.409738</v>
+        <v>111.988756</v>
       </c>
       <c r="G122" t="n">
-        <v>113.586878</v>
+        <v>114.595083</v>
       </c>
       <c r="H122" t="n">
-        <v>107.71948</v>
+        <v>108.391173</v>
       </c>
       <c r="I122" t="n">
-        <v>93.25534</v>
+        <v>93.712059</v>
       </c>
       <c r="J122" t="n">
-        <v>80.514917</v>
+        <v>80.853207</v>
       </c>
       <c r="K122" t="n">
-        <v>67.808939</v>
+        <v>68.068692</v>
       </c>
       <c r="L122" t="n">
-        <v>57.478287</v>
+        <v>57.685169</v>
       </c>
       <c r="M122" t="n">
-        <v>49.797875</v>
+        <v>49.968987</v>
       </c>
       <c r="N122" t="n">
-        <v>43.651169</v>
+        <v>43.794691</v>
       </c>
       <c r="O122" t="n">
-        <v>37.877833</v>
+        <v>37.994998</v>
       </c>
       <c r="P122" t="n">
-        <v>33.485795</v>
+        <v>33.581549</v>
       </c>
       <c r="Q122" t="n">
-        <v>29.031528</v>
+        <v>29.106291</v>
       </c>
       <c r="R122" t="n">
-        <v>24.093558</v>
+        <v>24.147977</v>
       </c>
       <c r="S122" t="n">
-        <v>19.875152</v>
+        <v>19.913452</v>
       </c>
       <c r="T122" t="n">
-        <v>15.404405</v>
+        <v>15.429166</v>
       </c>
       <c r="U122" t="n">
-        <v>10.438057</v>
+        <v>10.451743</v>
       </c>
       <c r="V122" t="n">
-        <v>6.077957</v>
+        <v>6.08422</v>
       </c>
     </row>
     <row r="123">
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.278783</v>
+        <v>0.328095</v>
       </c>
       <c r="F130" t="n">
-        <v>0.428544</v>
+        <v>0.472578</v>
       </c>
       <c r="G130" t="n">
-        <v>0.551959</v>
+        <v>0.588645</v>
       </c>
       <c r="H130" t="n">
-        <v>0.558288</v>
+        <v>0.581945</v>
       </c>
       <c r="I130" t="n">
-        <v>0.487409</v>
+        <v>0.497771</v>
       </c>
       <c r="J130" t="n">
         <v>0.405037</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.153559</v>
+        <v>0.161457</v>
       </c>
       <c r="F131" t="n">
-        <v>0.213234</v>
+        <v>0.221235</v>
       </c>
       <c r="G131" t="n">
-        <v>0.283252</v>
+        <v>0.290098</v>
       </c>
       <c r="H131" t="n">
-        <v>0.306833</v>
+        <v>0.311252</v>
       </c>
       <c r="I131" t="n">
-        <v>0.290279</v>
+        <v>0.292207</v>
       </c>
       <c r="J131" t="n">
         <v>0.260099</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>45.874073</v>
+        <v>45.986253</v>
       </c>
       <c r="F132" t="n">
-        <v>77.52021499999999</v>
+        <v>77.591962</v>
       </c>
       <c r="G132" t="n">
-        <v>110.312037</v>
+        <v>110.346604</v>
       </c>
       <c r="H132" t="n">
-        <v>123.378561</v>
+        <v>123.390469</v>
       </c>
       <c r="I132" t="n">
-        <v>117.027358</v>
+        <v>117.029824</v>
       </c>
       <c r="J132" t="n">
         <v>102.383971</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>95.471007</v>
+        <v>95.423458</v>
       </c>
       <c r="F133" t="n">
-        <v>99.768559</v>
+        <v>99.739997</v>
       </c>
       <c r="G133" t="n">
-        <v>94.826695</v>
+        <v>94.81698</v>
       </c>
       <c r="H133" t="n">
-        <v>86.817685</v>
+        <v>86.818119</v>
       </c>
       <c r="I133" t="n">
-        <v>78.541552</v>
+        <v>78.54293800000001</v>
       </c>
       <c r="J133" t="n">
         <v>72.984899</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.955286</v>
+        <v>0.970804</v>
       </c>
       <c r="F134" t="n">
-        <v>2.134903</v>
+        <v>2.146155</v>
       </c>
       <c r="G134" t="n">
-        <v>3.671476</v>
+        <v>3.678925</v>
       </c>
       <c r="H134" t="n">
-        <v>4.576423</v>
+        <v>4.580428</v>
       </c>
       <c r="I134" t="n">
-        <v>4.631704</v>
+        <v>4.633261</v>
       </c>
       <c r="J134" t="n">
         <v>4.263164</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>22.577731</v>
+        <v>22.564812</v>
       </c>
       <c r="F135" t="n">
-        <v>28.969887</v>
+        <v>28.956835</v>
       </c>
       <c r="G135" t="n">
-        <v>31.139868</v>
+        <v>31.129743</v>
       </c>
       <c r="H135" t="n">
-        <v>29.568379</v>
+        <v>29.562883</v>
       </c>
       <c r="I135" t="n">
-        <v>25.855658</v>
+        <v>25.853597</v>
       </c>
       <c r="J135" t="n">
         <v>22.077537</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.131699</v>
+        <v>0.154293</v>
       </c>
       <c r="F136" t="n">
-        <v>0.256812</v>
+        <v>0.274315</v>
       </c>
       <c r="G136" t="n">
-        <v>0.506514</v>
+        <v>0.518423</v>
       </c>
       <c r="H136" t="n">
-        <v>0.814455</v>
+        <v>0.8206830000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>1.033925</v>
+        <v>1.036233</v>
       </c>
       <c r="J136" t="n">
         <v>1.027066</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1.409844</v>
+        <v>1.415105</v>
       </c>
       <c r="F137" t="n">
-        <v>2.081018</v>
+        <v>2.085115</v>
       </c>
       <c r="G137" t="n">
-        <v>2.886479</v>
+        <v>2.88906</v>
       </c>
       <c r="H137" t="n">
-        <v>3.209453</v>
+        <v>3.210723</v>
       </c>
       <c r="I137" t="n">
-        <v>2.925017</v>
+        <v>2.925488</v>
       </c>
       <c r="J137" t="n">
         <v>2.399305</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.472094</v>
+        <v>0.490718</v>
       </c>
       <c r="F138" t="n">
-        <v>0.83579</v>
+        <v>0.850992</v>
       </c>
       <c r="G138" t="n">
-        <v>1.303689</v>
+        <v>1.314851</v>
       </c>
       <c r="H138" t="n">
-        <v>1.65387</v>
+        <v>1.660095</v>
       </c>
       <c r="I138" t="n">
-        <v>1.814884</v>
+        <v>1.817235</v>
       </c>
       <c r="J138" t="n">
         <v>1.835207</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1.503666</v>
+        <v>1.529754</v>
       </c>
       <c r="F139" t="n">
-        <v>2.608623</v>
+        <v>2.630826</v>
       </c>
       <c r="G139" t="n">
-        <v>3.534374</v>
+        <v>3.55226</v>
       </c>
       <c r="H139" t="n">
-        <v>3.695063</v>
+        <v>3.706469</v>
       </c>
       <c r="I139" t="n">
-        <v>3.322077</v>
+        <v>3.32706</v>
       </c>
       <c r="J139" t="n">
         <v>2.838769</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5.20134</v>
+        <v>5.343573</v>
       </c>
       <c r="F140" t="n">
-        <v>11.770946</v>
+        <v>11.880179</v>
       </c>
       <c r="G140" t="n">
-        <v>20.66352</v>
+        <v>20.742129</v>
       </c>
       <c r="H140" t="n">
-        <v>26.039487</v>
+        <v>26.085922</v>
       </c>
       <c r="I140" t="n">
-        <v>25.759603</v>
+        <v>25.779607</v>
       </c>
       <c r="J140" t="n">
         <v>22.659365</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>121.250916</v>
+        <v>121.154669</v>
       </c>
       <c r="F141" t="n">
-        <v>198.232608</v>
+        <v>198.104432</v>
       </c>
       <c r="G141" t="n">
-        <v>266.91018</v>
+        <v>266.77427</v>
       </c>
       <c r="H141" t="n">
-        <v>289.223761</v>
+        <v>289.129473</v>
       </c>
       <c r="I141" t="n">
-        <v>269.098246</v>
+        <v>269.056488</v>
       </c>
       <c r="J141" t="n">
         <v>236.613497</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>291.80381</v>
+        <v>291.560819</v>
       </c>
       <c r="F142" t="n">
-        <v>205.113184</v>
+        <v>204.979701</v>
       </c>
       <c r="G142" t="n">
-        <v>111.128924</v>
+        <v>111.076976</v>
       </c>
       <c r="H142" t="n">
-        <v>65.801619</v>
+        <v>65.785415</v>
       </c>
       <c r="I142" t="n">
-        <v>44.879872</v>
+        <v>44.875874</v>
       </c>
       <c r="J142" t="n">
         <v>35.822039</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7.074354</v>
+        <v>7.06648</v>
       </c>
       <c r="F146" t="n">
-        <v>11.312169</v>
+        <v>11.302892</v>
       </c>
       <c r="G146" t="n">
-        <v>15.185442</v>
+        <v>15.174827</v>
       </c>
       <c r="H146" t="n">
-        <v>15.315295</v>
+        <v>15.307442</v>
       </c>
       <c r="I146" t="n">
-        <v>12.289774</v>
+        <v>12.286472</v>
       </c>
       <c r="J146" t="n">
         <v>8.607609</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.384348</v>
+        <v>0.384775</v>
       </c>
       <c r="F147" t="n">
-        <v>0.470237</v>
+        <v>0.470626</v>
       </c>
       <c r="G147" t="n">
-        <v>0.516435</v>
+        <v>0.516736</v>
       </c>
       <c r="H147" t="n">
-        <v>0.507069</v>
+        <v>0.5072410000000001</v>
       </c>
       <c r="I147" t="n">
-        <v>0.444507</v>
+        <v>0.444573</v>
       </c>
       <c r="J147" t="n">
         <v>0.361039</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>41.48076</v>
+        <v>41.488206</v>
       </c>
       <c r="F148" t="n">
-        <v>51.042821</v>
+        <v>51.05171</v>
       </c>
       <c r="G148" t="n">
-        <v>51.827817</v>
+        <v>51.838131</v>
       </c>
       <c r="H148" t="n">
-        <v>47.607963</v>
+        <v>47.615645</v>
       </c>
       <c r="I148" t="n">
-        <v>40.969226</v>
+        <v>40.972461</v>
       </c>
       <c r="J148" t="n">
         <v>33.889741</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>21.982597</v>
+        <v>21.917574</v>
       </c>
       <c r="F149" t="n">
-        <v>27.389113</v>
+        <v>27.347613</v>
       </c>
       <c r="G149" t="n">
-        <v>30.2307</v>
+        <v>30.203924</v>
       </c>
       <c r="H149" t="n">
-        <v>29.948986</v>
+        <v>29.933814</v>
       </c>
       <c r="I149" t="n">
-        <v>24.588845</v>
+        <v>24.583022</v>
       </c>
       <c r="J149" t="n">
         <v>18.52167</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2.853853</v>
+        <v>2.940107</v>
       </c>
       <c r="F150" t="n">
-        <v>3.079397</v>
+        <v>3.126816</v>
       </c>
       <c r="G150" t="n">
-        <v>2.989186</v>
+        <v>3.016646</v>
       </c>
       <c r="H150" t="n">
-        <v>2.801419</v>
+        <v>2.816197</v>
       </c>
       <c r="I150" t="n">
-        <v>2.25116</v>
+        <v>2.256878</v>
       </c>
       <c r="J150" t="n">
         <v>1.671997</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>9.585896999999999</v>
+        <v>9.596424000000001</v>
       </c>
       <c r="F151" t="n">
-        <v>10.350253</v>
+        <v>10.357632</v>
       </c>
       <c r="G151" t="n">
-        <v>9.847089</v>
+        <v>9.852671000000001</v>
       </c>
       <c r="H151" t="n">
-        <v>9.027718999999999</v>
+        <v>9.031219</v>
       </c>
       <c r="I151" t="n">
-        <v>7.416383</v>
+        <v>7.417772</v>
       </c>
       <c r="J151" t="n">
         <v>5.809655</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>10.713698</v>
+        <v>10.734332</v>
       </c>
       <c r="F152" t="n">
-        <v>9.62907</v>
+        <v>9.647948</v>
       </c>
       <c r="G152" t="n">
-        <v>8.791029</v>
+        <v>8.80345</v>
       </c>
       <c r="H152" t="n">
-        <v>8.21269</v>
+        <v>8.219336999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>6.949294</v>
+        <v>6.951635</v>
       </c>
       <c r="J152" t="n">
         <v>5.507334</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>16.46129</v>
+        <v>16.403</v>
       </c>
       <c r="F153" t="n">
-        <v>20.312386</v>
+        <v>20.276401</v>
       </c>
       <c r="G153" t="n">
-        <v>20.821142</v>
+        <v>20.800113</v>
       </c>
       <c r="H153" t="n">
-        <v>19.305205</v>
+        <v>19.294176</v>
       </c>
       <c r="I153" t="n">
-        <v>15.320522</v>
+        <v>15.31642</v>
       </c>
       <c r="J153" t="n">
         <v>11.3794</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.516819</v>
+        <v>0.522715</v>
       </c>
       <c r="F154" t="n">
-        <v>0.438734</v>
+        <v>0.442543</v>
       </c>
       <c r="G154" t="n">
-        <v>0.370139</v>
+        <v>0.37248</v>
       </c>
       <c r="H154" t="n">
-        <v>0.320854</v>
+        <v>0.32213</v>
       </c>
       <c r="I154" t="n">
-        <v>0.257259</v>
+        <v>0.257735</v>
       </c>
       <c r="J154" t="n">
         <v>0.19837</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15.39776</v>
+        <v>15.376157</v>
       </c>
       <c r="F155" t="n">
-        <v>21.148208</v>
+        <v>21.13274</v>
       </c>
       <c r="G155" t="n">
-        <v>22.89767</v>
+        <v>22.888118</v>
       </c>
       <c r="H155" t="n">
-        <v>23.506401</v>
+        <v>23.500921</v>
       </c>
       <c r="I155" t="n">
-        <v>22.23395</v>
+        <v>22.231602</v>
       </c>
       <c r="J155" t="n">
         <v>20.427418</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15.28461</v>
+        <v>15.301151</v>
       </c>
       <c r="F156" t="n">
-        <v>17.790934</v>
+        <v>17.803635</v>
       </c>
       <c r="G156" t="n">
-        <v>16.392749</v>
+        <v>16.400733</v>
       </c>
       <c r="H156" t="n">
-        <v>14.579582</v>
+        <v>14.584129</v>
       </c>
       <c r="I156" t="n">
-        <v>12.169254</v>
+        <v>12.171174</v>
       </c>
       <c r="J156" t="n">
         <v>9.873715000000001</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.002956</v>
+        <v>0.003594</v>
       </c>
       <c r="F157" t="n">
-        <v>0.002197</v>
+        <v>0.002738</v>
       </c>
       <c r="G157" t="n">
-        <v>0.001396</v>
+        <v>0.001774</v>
       </c>
       <c r="H157" t="n">
-        <v>0.001016</v>
+        <v>0.001243</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0008050000000000001</v>
+        <v>0.0009</v>
       </c>
       <c r="J157" t="n">
         <v>0.000691</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.177657</v>
+        <v>0.187064</v>
       </c>
       <c r="F158" t="n">
-        <v>0.253679</v>
+        <v>0.25922</v>
       </c>
       <c r="G158" t="n">
-        <v>0.295497</v>
+        <v>0.29825</v>
       </c>
       <c r="H158" t="n">
-        <v>0.308728</v>
+        <v>0.310053</v>
       </c>
       <c r="I158" t="n">
-        <v>0.281142</v>
+        <v>0.281643</v>
       </c>
       <c r="J158" t="n">
         <v>0.23716</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.002123</v>
+        <v>0.002902</v>
       </c>
       <c r="F159" t="n">
-        <v>0.00261</v>
+        <v>0.003112</v>
       </c>
       <c r="G159" t="n">
-        <v>0.002547</v>
+        <v>0.002828</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0024</v>
+        <v>0.002548</v>
       </c>
       <c r="I159" t="n">
-        <v>0.002089</v>
+        <v>0.002148</v>
       </c>
       <c r="J159" t="n">
         <v>0.001777</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5.607924</v>
+        <v>5.602165</v>
       </c>
       <c r="F160" t="n">
-        <v>7.26489</v>
+        <v>7.261074</v>
       </c>
       <c r="G160" t="n">
-        <v>6.838487</v>
+        <v>6.836642</v>
       </c>
       <c r="H160" t="n">
-        <v>6.014721</v>
+        <v>6.013956</v>
       </c>
       <c r="I160" t="n">
-        <v>4.965099</v>
+        <v>4.964871</v>
       </c>
       <c r="J160" t="n">
         <v>4.193679</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.000831</v>
+        <v>0.001363</v>
       </c>
       <c r="F162" t="n">
-        <v>0.001976</v>
+        <v>0.00227</v>
       </c>
       <c r="G162" t="n">
-        <v>0.005124</v>
+        <v>0.005283</v>
       </c>
       <c r="H162" t="n">
-        <v>0.009785</v>
+        <v>0.009867000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>0.01285</v>
+        <v>0.012881</v>
       </c>
       <c r="J162" t="n">
         <v>0.013237</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.177652</v>
+        <v>0.177729</v>
       </c>
       <c r="F163" t="n">
-        <v>0.164303</v>
+        <v>0.164382</v>
       </c>
       <c r="G163" t="n">
-        <v>0.115415</v>
+        <v>0.115492</v>
       </c>
       <c r="H163" t="n">
-        <v>0.086439</v>
+        <v>0.086495</v>
       </c>
       <c r="I163" t="n">
-        <v>0.064757</v>
+        <v>0.06478299999999999</v>
       </c>
       <c r="J163" t="n">
         <v>0.050008</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>18.12595</v>
+        <v>18.122585</v>
       </c>
       <c r="F164" t="n">
-        <v>14.42187</v>
+        <v>14.420185</v>
       </c>
       <c r="G164" t="n">
-        <v>9.308885999999999</v>
+        <v>9.30828</v>
       </c>
       <c r="H164" t="n">
-        <v>6.247635</v>
+        <v>6.247501</v>
       </c>
       <c r="I164" t="n">
-        <v>4.140814</v>
+        <v>4.14082</v>
       </c>
       <c r="J164" t="n">
         <v>2.85707</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3.219139</v>
+        <v>3.219077</v>
       </c>
       <c r="F165" t="n">
-        <v>3.962</v>
+        <v>3.961935</v>
       </c>
       <c r="G165" t="n">
-        <v>5.265699</v>
+        <v>5.265461</v>
       </c>
       <c r="H165" t="n">
-        <v>6.403528</v>
+        <v>6.403228</v>
       </c>
       <c r="I165" t="n">
-        <v>6.486287</v>
+        <v>6.486095</v>
       </c>
       <c r="J165" t="n">
         <v>5.970508</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>198.176497</v>
+        <v>198.134406</v>
       </c>
       <c r="F166" t="n">
-        <v>236.617275</v>
+        <v>236.580895</v>
       </c>
       <c r="G166" t="n">
-        <v>233.228576</v>
+        <v>233.200238</v>
       </c>
       <c r="H166" t="n">
-        <v>215.997859</v>
+        <v>215.979254</v>
       </c>
       <c r="I166" t="n">
-        <v>179.445157</v>
+        <v>179.436847</v>
       </c>
       <c r="J166" t="n">
         <v>142.035265</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.62471</v>
+        <v>0.64285</v>
       </c>
       <c r="F167" t="n">
-        <v>0.984745</v>
+        <v>0.9988359999999999</v>
       </c>
       <c r="G167" t="n">
-        <v>1.215646</v>
+        <v>1.226224</v>
       </c>
       <c r="H167" t="n">
-        <v>1.280222</v>
+        <v>1.287175</v>
       </c>
       <c r="I167" t="n">
-        <v>1.131419</v>
+        <v>1.134559</v>
       </c>
       <c r="J167" t="n">
         <v>0.925998</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.028872</v>
+        <v>0.029191</v>
       </c>
       <c r="F168" t="n">
-        <v>0.036086</v>
+        <v>0.036358</v>
       </c>
       <c r="G168" t="n">
-        <v>0.037307</v>
+        <v>0.037526</v>
       </c>
       <c r="H168" t="n">
-        <v>0.036215</v>
+        <v>0.036364</v>
       </c>
       <c r="I168" t="n">
-        <v>0.031646</v>
+        <v>0.031713</v>
       </c>
       <c r="J168" t="n">
         <v>0.026375</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>64.9689</v>
+        <v>64.962811</v>
       </c>
       <c r="F169" t="n">
-        <v>95.555437</v>
+        <v>95.547116</v>
       </c>
       <c r="G169" t="n">
-        <v>117.340234</v>
+        <v>117.330947</v>
       </c>
       <c r="H169" t="n">
-        <v>123.646009</v>
+        <v>123.638788</v>
       </c>
       <c r="I169" t="n">
-        <v>107.073447</v>
+        <v>107.07014</v>
       </c>
       <c r="J169" t="n">
         <v>84.93428400000001</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3.308782</v>
+        <v>3.308487</v>
       </c>
       <c r="F170" t="n">
-        <v>2.741486</v>
+        <v>2.741505</v>
       </c>
       <c r="G170" t="n">
-        <v>2.175585</v>
+        <v>2.17574</v>
       </c>
       <c r="H170" t="n">
-        <v>1.916761</v>
+        <v>1.916911</v>
       </c>
       <c r="I170" t="n">
-        <v>1.655306</v>
+        <v>1.655381</v>
       </c>
       <c r="J170" t="n">
         <v>1.432627</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2.634958</v>
+        <v>2.636745</v>
       </c>
       <c r="F171" t="n">
-        <v>3.137579</v>
+        <v>3.139001</v>
       </c>
       <c r="G171" t="n">
-        <v>3.094282</v>
+        <v>3.095368</v>
       </c>
       <c r="H171" t="n">
-        <v>2.865763</v>
+        <v>2.866463</v>
       </c>
       <c r="I171" t="n">
-        <v>2.386394</v>
+        <v>2.386693</v>
       </c>
       <c r="J171" t="n">
         <v>1.893242</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.005243</v>
+        <v>0.00923</v>
       </c>
       <c r="F172" t="n">
-        <v>0.005653</v>
+        <v>0.008762000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>0.005968</v>
+        <v>0.008203</v>
       </c>
       <c r="H172" t="n">
-        <v>0.00609</v>
+        <v>0.007464</v>
       </c>
       <c r="I172" t="n">
-        <v>0.005417</v>
+        <v>0.005999</v>
       </c>
       <c r="J172" t="n">
         <v>0.004464</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.6840619999999999</v>
+        <v>0.683936</v>
       </c>
       <c r="F173" t="n">
-        <v>0.680101</v>
+        <v>0.680018</v>
       </c>
       <c r="G173" t="n">
-        <v>0.612989</v>
+        <v>0.612935</v>
       </c>
       <c r="H173" t="n">
-        <v>0.586276</v>
+        <v>0.58624</v>
       </c>
       <c r="I173" t="n">
-        <v>0.523595</v>
+        <v>0.523578</v>
       </c>
       <c r="J173" t="n">
         <v>0.45687</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3.215143</v>
+        <v>3.234651</v>
       </c>
       <c r="F174" t="n">
-        <v>4.412075</v>
+        <v>4.427034</v>
       </c>
       <c r="G174" t="n">
-        <v>4.911239</v>
+        <v>4.922191</v>
       </c>
       <c r="H174" t="n">
-        <v>4.808722</v>
+        <v>4.815693</v>
       </c>
       <c r="I174" t="n">
-        <v>3.989193</v>
+        <v>3.992238</v>
       </c>
       <c r="J174" t="n">
         <v>2.941444</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4.568816</v>
+        <v>4.567863</v>
       </c>
       <c r="F175" t="n">
-        <v>3.042403</v>
+        <v>3.04198</v>
       </c>
       <c r="G175" t="n">
-        <v>1.891822</v>
+        <v>1.891648</v>
       </c>
       <c r="H175" t="n">
-        <v>1.316056</v>
+        <v>1.315993</v>
       </c>
       <c r="I175" t="n">
-        <v>0.889592</v>
+        <v>0.889579</v>
       </c>
       <c r="J175" t="n">
         <v>0.6193340000000001</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.005611</v>
+        <v>0.00562</v>
       </c>
       <c r="F176" t="n">
-        <v>0.009303000000000001</v>
+        <v>0.009308</v>
       </c>
       <c r="G176" t="n">
-        <v>0.011241</v>
+        <v>0.011245</v>
       </c>
       <c r="H176" t="n">
-        <v>0.011431</v>
+        <v>0.011433</v>
       </c>
       <c r="I176" t="n">
-        <v>0.00953</v>
+        <v>0.009531</v>
       </c>
       <c r="J176" t="n">
         <v>0.007408</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>26.917026</v>
+        <v>26.925619</v>
       </c>
       <c r="F177" t="n">
-        <v>17.303184</v>
+        <v>17.31587</v>
       </c>
       <c r="G177" t="n">
-        <v>10.719528</v>
+        <v>10.732742</v>
       </c>
       <c r="H177" t="n">
-        <v>7.786275</v>
+        <v>7.796185</v>
       </c>
       <c r="I177" t="n">
-        <v>5.984169</v>
+        <v>5.988731</v>
       </c>
       <c r="J177" t="n">
         <v>4.809409</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.018365</v>
+        <v>0.018372</v>
       </c>
       <c r="F178" t="n">
-        <v>0.022992</v>
+        <v>0.022999</v>
       </c>
       <c r="G178" t="n">
-        <v>0.025249</v>
+        <v>0.025254</v>
       </c>
       <c r="H178" t="n">
-        <v>0.026355</v>
+        <v>0.026359</v>
       </c>
       <c r="I178" t="n">
-        <v>0.024568</v>
+        <v>0.02457</v>
       </c>
       <c r="J178" t="n">
         <v>0.021726</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.013416</v>
+        <v>0.013437</v>
       </c>
       <c r="F179" t="n">
-        <v>0.017027</v>
+        <v>0.017043</v>
       </c>
       <c r="G179" t="n">
-        <v>0.016611</v>
+        <v>0.016624</v>
       </c>
       <c r="H179" t="n">
-        <v>0.015049</v>
+        <v>0.015058</v>
       </c>
       <c r="I179" t="n">
-        <v>0.011897</v>
+        <v>0.011901</v>
       </c>
       <c r="J179" t="n">
         <v>0.008795000000000001</v>
@@ -14130,52 +14130,52 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-1e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>3e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>-5e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="H181" t="n">
+        <v>-8e-06</v>
+      </c>
+      <c r="I181" t="n">
         <v>-0</v>
       </c>
-      <c r="I181" t="n">
-        <v>8e-06</v>
-      </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>-2e-06</v>
       </c>
       <c r="K181" t="n">
-        <v>1e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>-2e-06</v>
       </c>
       <c r="M181" t="n">
-        <v>1e-06</v>
+        <v>-0</v>
       </c>
       <c r="N181" t="n">
-        <v>-5e-06</v>
+        <v>-7e-06</v>
       </c>
       <c r="O181" t="n">
         <v>-0</v>
       </c>
       <c r="P181" t="n">
-        <v>2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="Q181" t="n">
-        <v>-7e-06</v>
+        <v>-8e-06</v>
       </c>
       <c r="R181" t="n">
-        <v>2e-06</v>
+        <v>-0</v>
       </c>
       <c r="S181" t="n">
-        <v>-1e-06</v>
+        <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>3e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="U181" t="n">
         <v>1e-06</v>
